--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="337">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -751,6 +751,9 @@
     <t>['90+5']</t>
   </si>
   <si>
+    <t>['2', '68']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1019,6 +1022,9 @@
   </si>
   <si>
     <t>['49', '71', '85']</t>
+  </si>
+  <si>
+    <t>['71', '76']</t>
   </si>
 </sst>
 </file>
@@ -1380,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP232"/>
+  <dimension ref="A1:BP234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1636,7 +1642,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2048,7 +2054,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2538,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ6">
         <v>1</v>
@@ -2666,7 +2672,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2872,7 +2878,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3078,7 +3084,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3365,7 +3371,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ10">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3902,7 +3908,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4108,7 +4114,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4598,7 +4604,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ16">
         <v>1.5</v>
@@ -5138,7 +5144,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5422,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ20">
         <v>1.3</v>
@@ -5756,7 +5762,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5962,7 +5968,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6168,7 +6174,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6374,7 +6380,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6455,7 +6461,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ25">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6580,7 +6586,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6786,7 +6792,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7198,7 +7204,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7816,7 +7822,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -7897,7 +7903,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ32">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR32">
         <v>1.31</v>
@@ -8022,7 +8028,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8434,7 +8440,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8515,7 +8521,7 @@
         <v>1</v>
       </c>
       <c r="AQ35">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR35">
         <v>1.42</v>
@@ -9052,7 +9058,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9542,7 +9548,7 @@
         <v>1</v>
       </c>
       <c r="AP40">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ40">
         <v>1.4</v>
@@ -10288,7 +10294,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10572,7 +10578,7 @@
         <v>1</v>
       </c>
       <c r="AP45">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ45">
         <v>0.5</v>
@@ -10906,7 +10912,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -12017,7 +12023,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ52">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR52">
         <v>1.28</v>
@@ -12554,7 +12560,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12760,7 +12766,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -12966,7 +12972,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13172,7 +13178,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13250,7 +13256,7 @@
         <v>1</v>
       </c>
       <c r="AP58">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ58">
         <v>1.09</v>
@@ -13584,7 +13590,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14202,7 +14208,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14489,7 +14495,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ64">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR64">
         <v>1.39</v>
@@ -14820,7 +14826,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15232,7 +15238,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15310,7 +15316,7 @@
         <v>0.33</v>
       </c>
       <c r="AP68">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ68">
         <v>1.22</v>
@@ -15438,7 +15444,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16056,7 +16062,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16262,7 +16268,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16468,7 +16474,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17292,7 +17298,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17373,7 +17379,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ78">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR78">
         <v>1.42</v>
@@ -17498,7 +17504,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17782,7 +17788,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ80">
         <v>1.3</v>
@@ -17910,7 +17916,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18116,7 +18122,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18322,7 +18328,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18403,7 +18409,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ83">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR83">
         <v>1.8</v>
@@ -18815,7 +18821,7 @@
         <v>1</v>
       </c>
       <c r="AQ85">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR85">
         <v>1.38</v>
@@ -19146,7 +19152,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19558,7 +19564,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19636,7 +19642,7 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ89">
         <v>0.45</v>
@@ -19764,7 +19770,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20176,7 +20182,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20588,7 +20594,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20794,7 +20800,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21824,7 +21830,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22111,7 +22117,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ101">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR101">
         <v>1.58</v>
@@ -23266,7 +23272,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23347,7 +23353,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ107">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR107">
         <v>1.53</v>
@@ -23550,7 +23556,7 @@
         <v>1.5</v>
       </c>
       <c r="AP108">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ108">
         <v>1.27</v>
@@ -23884,7 +23890,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24168,7 +24174,7 @@
         <v>1.75</v>
       </c>
       <c r="AP111">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ111">
         <v>0.82</v>
@@ -24296,7 +24302,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24502,7 +24508,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24914,7 +24920,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25738,7 +25744,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26356,7 +26362,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26768,7 +26774,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -26849,7 +26855,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ124">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR124">
         <v>1.12</v>
@@ -27180,7 +27186,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27592,7 +27598,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27673,7 +27679,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ128">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR128">
         <v>1.61</v>
@@ -28004,7 +28010,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28082,7 +28088,7 @@
         <v>1</v>
       </c>
       <c r="AP130">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ130">
         <v>1.1</v>
@@ -28210,7 +28216,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28416,7 +28422,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28622,7 +28628,7 @@
         <v>106</v>
       </c>
       <c r="P133" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q133">
         <v>3.1</v>
@@ -28700,7 +28706,7 @@
         <v>0.2</v>
       </c>
       <c r="AP133">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ133">
         <v>0.18</v>
@@ -28828,7 +28834,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29034,7 +29040,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29652,7 +29658,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30270,7 +30276,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30476,7 +30482,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30682,7 +30688,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30888,7 +30894,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31175,7 +31181,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ145">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR145">
         <v>1.15</v>
@@ -31300,7 +31306,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31712,7 +31718,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -31790,10 +31796,10 @@
         <v>3</v>
       </c>
       <c r="AP148">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ148">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR148">
         <v>1.13</v>
@@ -31996,7 +32002,7 @@
         <v>1</v>
       </c>
       <c r="AP149">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ149">
         <v>1.27</v>
@@ -32742,7 +32748,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33360,7 +33366,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -34880,7 +34886,7 @@
         <v>1.43</v>
       </c>
       <c r="AP163">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ163">
         <v>1.36</v>
@@ -35008,7 +35014,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35626,7 +35632,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35913,7 +35919,7 @@
         <v>1.9</v>
       </c>
       <c r="AQ168">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR168">
         <v>1.29</v>
@@ -36038,7 +36044,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36116,7 +36122,7 @@
         <v>0.29</v>
       </c>
       <c r="AP169">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ169">
         <v>0.18</v>
@@ -36656,7 +36662,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37274,7 +37280,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37686,7 +37692,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38098,7 +38104,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38304,7 +38310,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39128,7 +39134,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39827,7 +39833,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ187">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR187">
         <v>1.45</v>
@@ -39952,7 +39958,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40445,7 +40451,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ190">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR190">
         <v>1.74</v>
@@ -40570,7 +40576,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40776,7 +40782,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -40982,7 +40988,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41060,7 +41066,7 @@
         <v>0.89</v>
       </c>
       <c r="AP193">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ193">
         <v>1.27</v>
@@ -41188,7 +41194,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41472,7 +41478,7 @@
         <v>1.75</v>
       </c>
       <c r="AP195">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ195">
         <v>1.5</v>
@@ -42424,7 +42430,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42836,7 +42842,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -42917,7 +42923,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ202">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR202">
         <v>1.63</v>
@@ -43042,7 +43048,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43660,7 +43666,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44072,7 +44078,7 @@
         <v>94</v>
       </c>
       <c r="P208" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44359,7 +44365,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ209">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AR209">
         <v>1.74</v>
@@ -44562,7 +44568,7 @@
         <v>1.22</v>
       </c>
       <c r="AP210">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ210">
         <v>1.36</v>
@@ -44690,7 +44696,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -44896,7 +44902,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45102,7 +45108,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45180,7 +45186,7 @@
         <v>1.5</v>
       </c>
       <c r="AP213">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AQ213">
         <v>1.64</v>
@@ -45308,7 +45314,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45720,7 +45726,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46007,7 +46013,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ217">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AR217">
         <v>1.61</v>
@@ -46956,7 +46962,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47368,7 +47374,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47780,7 +47786,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -47986,7 +47992,7 @@
         <v>200</v>
       </c>
       <c r="P227" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q227">
         <v>2.25</v>
@@ -48398,7 +48404,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48604,7 +48610,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48810,7 +48816,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49173,6 +49179,418 @@
       </c>
       <c r="BP232">
         <v>1.22</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7728437</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45668.41666666666</v>
+      </c>
+      <c r="F233">
+        <v>22</v>
+      </c>
+      <c r="G233" t="s">
+        <v>74</v>
+      </c>
+      <c r="H233" t="s">
+        <v>87</v>
+      </c>
+      <c r="I233">
+        <v>0</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>0</v>
+      </c>
+      <c r="L233">
+        <v>0</v>
+      </c>
+      <c r="M233">
+        <v>0</v>
+      </c>
+      <c r="N233">
+        <v>0</v>
+      </c>
+      <c r="O233" t="s">
+        <v>94</v>
+      </c>
+      <c r="P233" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q233">
+        <v>2.63</v>
+      </c>
+      <c r="R233">
+        <v>1.95</v>
+      </c>
+      <c r="S233">
+        <v>5.5</v>
+      </c>
+      <c r="T233">
+        <v>1.57</v>
+      </c>
+      <c r="U233">
+        <v>2.25</v>
+      </c>
+      <c r="V233">
+        <v>3.75</v>
+      </c>
+      <c r="W233">
+        <v>1.25</v>
+      </c>
+      <c r="X233">
+        <v>11</v>
+      </c>
+      <c r="Y233">
+        <v>1.05</v>
+      </c>
+      <c r="Z233">
+        <v>1.77</v>
+      </c>
+      <c r="AA233">
+        <v>3.1</v>
+      </c>
+      <c r="AB233">
+        <v>4.75</v>
+      </c>
+      <c r="AC233">
+        <v>1.09</v>
+      </c>
+      <c r="AD233">
+        <v>7</v>
+      </c>
+      <c r="AE233">
+        <v>1.5</v>
+      </c>
+      <c r="AF233">
+        <v>2.4</v>
+      </c>
+      <c r="AG233">
+        <v>2.48</v>
+      </c>
+      <c r="AH233">
+        <v>1.47</v>
+      </c>
+      <c r="AI233">
+        <v>2.25</v>
+      </c>
+      <c r="AJ233">
+        <v>1.57</v>
+      </c>
+      <c r="AK233">
+        <v>1.19</v>
+      </c>
+      <c r="AL233">
+        <v>1.34</v>
+      </c>
+      <c r="AM233">
+        <v>1.87</v>
+      </c>
+      <c r="AN233">
+        <v>0.73</v>
+      </c>
+      <c r="AO233">
+        <v>0.55</v>
+      </c>
+      <c r="AP233">
+        <v>0.75</v>
+      </c>
+      <c r="AQ233">
+        <v>0.58</v>
+      </c>
+      <c r="AR233">
+        <v>1.18</v>
+      </c>
+      <c r="AS233">
+        <v>0.97</v>
+      </c>
+      <c r="AT233">
+        <v>2.15</v>
+      </c>
+      <c r="AU233">
+        <v>6</v>
+      </c>
+      <c r="AV233">
+        <v>3</v>
+      </c>
+      <c r="AW233">
+        <v>13</v>
+      </c>
+      <c r="AX233">
+        <v>2</v>
+      </c>
+      <c r="AY233">
+        <v>21</v>
+      </c>
+      <c r="AZ233">
+        <v>5</v>
+      </c>
+      <c r="BA233">
+        <v>8</v>
+      </c>
+      <c r="BB233">
+        <v>2</v>
+      </c>
+      <c r="BC233">
+        <v>10</v>
+      </c>
+      <c r="BD233">
+        <v>1.38</v>
+      </c>
+      <c r="BE233">
+        <v>7</v>
+      </c>
+      <c r="BF233">
+        <v>3.4</v>
+      </c>
+      <c r="BG233">
+        <v>1.37</v>
+      </c>
+      <c r="BH233">
+        <v>2.75</v>
+      </c>
+      <c r="BI233">
+        <v>1.64</v>
+      </c>
+      <c r="BJ233">
+        <v>2.07</v>
+      </c>
+      <c r="BK233">
+        <v>2.04</v>
+      </c>
+      <c r="BL233">
+        <v>1.66</v>
+      </c>
+      <c r="BM233">
+        <v>2.63</v>
+      </c>
+      <c r="BN233">
+        <v>1.41</v>
+      </c>
+      <c r="BO233">
+        <v>3.4</v>
+      </c>
+      <c r="BP233">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7728430</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45668.51041666666</v>
+      </c>
+      <c r="F234">
+        <v>22</v>
+      </c>
+      <c r="G234" t="s">
+        <v>85</v>
+      </c>
+      <c r="H234" t="s">
+        <v>77</v>
+      </c>
+      <c r="I234">
+        <v>1</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>1</v>
+      </c>
+      <c r="L234">
+        <v>2</v>
+      </c>
+      <c r="M234">
+        <v>2</v>
+      </c>
+      <c r="N234">
+        <v>4</v>
+      </c>
+      <c r="O234" t="s">
+        <v>245</v>
+      </c>
+      <c r="P234" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q234">
+        <v>2.75</v>
+      </c>
+      <c r="R234">
+        <v>2.2</v>
+      </c>
+      <c r="S234">
+        <v>3.75</v>
+      </c>
+      <c r="T234">
+        <v>1.4</v>
+      </c>
+      <c r="U234">
+        <v>2.75</v>
+      </c>
+      <c r="V234">
+        <v>2.75</v>
+      </c>
+      <c r="W234">
+        <v>1.4</v>
+      </c>
+      <c r="X234">
+        <v>8</v>
+      </c>
+      <c r="Y234">
+        <v>1.08</v>
+      </c>
+      <c r="Z234">
+        <v>2.12</v>
+      </c>
+      <c r="AA234">
+        <v>3.44</v>
+      </c>
+      <c r="AB234">
+        <v>3.44</v>
+      </c>
+      <c r="AC234">
+        <v>1.06</v>
+      </c>
+      <c r="AD234">
+        <v>8.5</v>
+      </c>
+      <c r="AE234">
+        <v>1.3</v>
+      </c>
+      <c r="AF234">
+        <v>3.3</v>
+      </c>
+      <c r="AG234">
+        <v>1.94</v>
+      </c>
+      <c r="AH234">
+        <v>1.87</v>
+      </c>
+      <c r="AI234">
+        <v>1.73</v>
+      </c>
+      <c r="AJ234">
+        <v>2</v>
+      </c>
+      <c r="AK234">
+        <v>1.32</v>
+      </c>
+      <c r="AL234">
+        <v>1.31</v>
+      </c>
+      <c r="AM234">
+        <v>1.66</v>
+      </c>
+      <c r="AN234">
+        <v>1.4</v>
+      </c>
+      <c r="AO234">
+        <v>2.2</v>
+      </c>
+      <c r="AP234">
+        <v>1.36</v>
+      </c>
+      <c r="AQ234">
+        <v>2.09</v>
+      </c>
+      <c r="AR234">
+        <v>1.56</v>
+      </c>
+      <c r="AS234">
+        <v>1.38</v>
+      </c>
+      <c r="AT234">
+        <v>2.94</v>
+      </c>
+      <c r="AU234">
+        <v>-1</v>
+      </c>
+      <c r="AV234">
+        <v>-1</v>
+      </c>
+      <c r="AW234">
+        <v>-1</v>
+      </c>
+      <c r="AX234">
+        <v>-1</v>
+      </c>
+      <c r="AY234">
+        <v>-1</v>
+      </c>
+      <c r="AZ234">
+        <v>-1</v>
+      </c>
+      <c r="BA234">
+        <v>-1</v>
+      </c>
+      <c r="BB234">
+        <v>-1</v>
+      </c>
+      <c r="BC234">
+        <v>-1</v>
+      </c>
+      <c r="BD234">
+        <v>1.86</v>
+      </c>
+      <c r="BE234">
+        <v>6.4</v>
+      </c>
+      <c r="BF234">
+        <v>2.15</v>
+      </c>
+      <c r="BG234">
+        <v>1.37</v>
+      </c>
+      <c r="BH234">
+        <v>2.75</v>
+      </c>
+      <c r="BI234">
+        <v>1.63</v>
+      </c>
+      <c r="BJ234">
+        <v>2.08</v>
+      </c>
+      <c r="BK234">
+        <v>2.02</v>
+      </c>
+      <c r="BL234">
+        <v>1.67</v>
+      </c>
+      <c r="BM234">
+        <v>2.55</v>
+      </c>
+      <c r="BN234">
+        <v>1.43</v>
+      </c>
+      <c r="BO234">
+        <v>3.4</v>
+      </c>
+      <c r="BP234">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="338">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -754,6 +754,9 @@
     <t>['2', '68']</t>
   </si>
   <si>
+    <t>['35', '60']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1386,7 +1389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP234"/>
+  <dimension ref="A1:BP238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1642,7 +1645,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2054,7 +2057,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2341,7 +2344,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ5">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2672,7 +2675,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2878,7 +2881,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3084,7 +3087,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3908,7 +3911,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4114,7 +4117,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4192,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -5016,10 +5019,10 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ18">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5144,7 +5147,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5222,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="AP19">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ19">
         <v>1.64</v>
@@ -5762,7 +5765,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5968,7 +5971,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6174,7 +6177,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6380,7 +6383,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6458,7 +6461,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ25">
         <v>2.09</v>
@@ -6586,7 +6589,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6792,7 +6795,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6870,7 +6873,7 @@
         <v>3</v>
       </c>
       <c r="AP27">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ27">
         <v>1.09</v>
@@ -7079,7 +7082,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ28">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR28">
         <v>0</v>
@@ -7204,7 +7207,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7285,7 +7288,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ29">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR29">
         <v>1.44</v>
@@ -7822,7 +7825,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8028,7 +8031,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8440,7 +8443,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8518,7 +8521,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ35">
         <v>2.09</v>
@@ -8727,7 +8730,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ36">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR36">
         <v>2.09</v>
@@ -8930,7 +8933,7 @@
         <v>1</v>
       </c>
       <c r="AP37">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ37">
         <v>0.82</v>
@@ -9058,7 +9061,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9551,7 +9554,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ40">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR40">
         <v>1.37</v>
@@ -10294,7 +10297,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10787,7 +10790,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ46">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR46">
         <v>1.47</v>
@@ -10912,7 +10915,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11402,7 +11405,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ49">
         <v>1.27</v>
@@ -11611,7 +11614,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ50">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR50">
         <v>1.56</v>
@@ -12020,7 +12023,7 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ52">
         <v>0.58</v>
@@ -12560,7 +12563,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12766,7 +12769,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -12847,7 +12850,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ56">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR56">
         <v>1.94</v>
@@ -12972,7 +12975,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13178,7 +13181,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13590,7 +13593,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14080,10 +14083,10 @@
         <v>0.5</v>
       </c>
       <c r="AP62">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ62">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR62">
         <v>1.36</v>
@@ -14208,7 +14211,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14701,7 +14704,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ65">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR65">
         <v>1.25</v>
@@ -14826,7 +14829,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15110,7 +15113,7 @@
         <v>0</v>
       </c>
       <c r="AP67">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ67">
         <v>0.45</v>
@@ -15238,7 +15241,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15319,7 +15322,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ68">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR68">
         <v>1.07</v>
@@ -15444,7 +15447,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16062,7 +16065,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16140,7 +16143,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ72">
         <v>1.3</v>
@@ -16268,7 +16271,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16474,7 +16477,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17170,7 +17173,7 @@
         <v>1.67</v>
       </c>
       <c r="AP77">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ77">
         <v>0.5</v>
@@ -17298,7 +17301,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17504,7 +17507,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17582,7 +17585,7 @@
         <v>2.33</v>
       </c>
       <c r="AP79">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
         <v>1</v>
@@ -17916,7 +17919,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18122,7 +18125,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18203,7 +18206,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ82">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR82">
         <v>1.41</v>
@@ -18328,7 +18331,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18818,7 +18821,7 @@
         <v>1.5</v>
       </c>
       <c r="AP85">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ85">
         <v>0.58</v>
@@ -19152,7 +19155,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19233,7 +19236,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ87">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR87">
         <v>1.47</v>
@@ -19564,7 +19567,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19770,7 +19773,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -19848,7 +19851,7 @@
         <v>1.4</v>
       </c>
       <c r="AP90">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ90">
         <v>1.45</v>
@@ -20182,7 +20185,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20594,7 +20597,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20672,7 +20675,7 @@
         <v>1.5</v>
       </c>
       <c r="AP94">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
         <v>1.09</v>
@@ -20800,7 +20803,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -20878,7 +20881,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ95">
         <v>1.64</v>
@@ -21499,7 +21502,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ98">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR98">
         <v>1.35</v>
@@ -21705,7 +21708,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ99">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR99">
         <v>1.46</v>
@@ -21830,7 +21833,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21911,7 +21914,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ100">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR100">
         <v>1.65</v>
@@ -22320,7 +22323,7 @@
         <v>1.2</v>
       </c>
       <c r="AP102">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ102">
         <v>1.27</v>
@@ -23272,7 +23275,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23765,7 +23768,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ109">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR109">
         <v>1.4</v>
@@ -23890,7 +23893,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24302,7 +24305,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24380,10 +24383,10 @@
         <v>1.25</v>
       </c>
       <c r="AP112">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ112">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR112">
         <v>1.61</v>
@@ -24508,7 +24511,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24920,7 +24923,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25744,7 +25747,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -25825,7 +25828,7 @@
         <v>2</v>
       </c>
       <c r="AQ119">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR119">
         <v>1.68</v>
@@ -26234,7 +26237,7 @@
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ121">
         <v>1</v>
@@ -26362,7 +26365,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26774,7 +26777,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27186,7 +27189,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27267,7 +27270,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ126">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR126">
         <v>1.8</v>
@@ -27470,7 +27473,7 @@
         <v>1</v>
       </c>
       <c r="AP127">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ127">
         <v>0.5</v>
@@ -27598,7 +27601,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28010,7 +28013,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28091,7 +28094,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ130">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR130">
         <v>1.64</v>
@@ -28216,7 +28219,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28294,7 +28297,7 @@
         <v>1.17</v>
       </c>
       <c r="AP131">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ131">
         <v>1.64</v>
@@ -28422,7 +28425,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28628,7 +28631,7 @@
         <v>106</v>
       </c>
       <c r="P133" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q133">
         <v>3.1</v>
@@ -28834,7 +28837,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29040,7 +29043,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29121,7 +29124,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ135">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR135">
         <v>1.12</v>
@@ -29658,7 +29661,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -29942,7 +29945,7 @@
         <v>1.17</v>
       </c>
       <c r="AP139">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ139">
         <v>0.82</v>
@@ -30148,10 +30151,10 @@
         <v>1</v>
       </c>
       <c r="AP140">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ140">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR140">
         <v>1.34</v>
@@ -30276,7 +30279,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30482,7 +30485,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30688,7 +30691,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30766,7 +30769,7 @@
         <v>1.86</v>
       </c>
       <c r="AP143">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ143">
         <v>1.45</v>
@@ -30894,7 +30897,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31178,7 +31181,7 @@
         <v>0.86</v>
       </c>
       <c r="AP145">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ145">
         <v>0.58</v>
@@ -31306,7 +31309,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31387,7 +31390,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ146">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR146">
         <v>1.62</v>
@@ -31593,7 +31596,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ147">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR147">
         <v>1.4</v>
@@ -31718,7 +31721,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32748,7 +32751,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32829,7 +32832,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ153">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR153">
         <v>1.58</v>
@@ -33366,7 +33369,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33856,7 +33859,7 @@
         <v>0.33</v>
       </c>
       <c r="AP158">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ158">
         <v>0.18</v>
@@ -34065,7 +34068,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ159">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR159">
         <v>1.75</v>
@@ -35014,7 +35017,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35632,7 +35635,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -35916,7 +35919,7 @@
         <v>3</v>
       </c>
       <c r="AP168">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ168">
         <v>2.09</v>
@@ -36044,7 +36047,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36331,7 +36334,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ170">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR170">
         <v>1.57</v>
@@ -36662,7 +36665,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -36740,10 +36743,10 @@
         <v>1.86</v>
       </c>
       <c r="AP172">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ172">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR172">
         <v>1.15</v>
@@ -37280,7 +37283,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37692,7 +37695,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -37770,7 +37773,7 @@
         <v>0.88</v>
       </c>
       <c r="AP177">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ177">
         <v>1.27</v>
@@ -38104,7 +38107,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38310,7 +38313,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38391,7 +38394,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ180">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AR180">
         <v>1.48</v>
@@ -38597,7 +38600,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ181">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR181">
         <v>1.48</v>
@@ -38800,7 +38803,7 @@
         <v>1.14</v>
       </c>
       <c r="AP182">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ182">
         <v>1.3</v>
@@ -39134,7 +39137,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39958,7 +39961,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40576,7 +40579,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40782,7 +40785,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -40860,7 +40863,7 @@
         <v>0.63</v>
       </c>
       <c r="AP192">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ192">
         <v>0.5</v>
@@ -40988,7 +40991,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41194,7 +41197,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41272,7 +41275,7 @@
         <v>1.56</v>
       </c>
       <c r="AP194">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ194">
         <v>1.64</v>
@@ -41481,7 +41484,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ195">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR195">
         <v>1.66</v>
@@ -42099,7 +42102,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ198">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR198">
         <v>1.19</v>
@@ -42305,7 +42308,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ199">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR199">
         <v>1.74</v>
@@ -42430,7 +42433,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42842,7 +42845,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43048,7 +43051,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43538,7 +43541,7 @@
         <v>1.75</v>
       </c>
       <c r="AP205">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ205">
         <v>1.5</v>
@@ -43666,7 +43669,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44078,7 +44081,7 @@
         <v>94</v>
       </c>
       <c r="P208" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44696,7 +44699,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -44902,7 +44905,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45108,7 +45111,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45314,7 +45317,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45395,7 +45398,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ214">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AR214">
         <v>1.17</v>
@@ -45598,7 +45601,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP215">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AQ215">
         <v>0.55</v>
@@ -45726,7 +45729,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46219,7 +46222,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ218">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR218">
         <v>1.41</v>
@@ -46422,7 +46425,7 @@
         <v>0.22</v>
       </c>
       <c r="AP219">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AQ219">
         <v>0.18</v>
@@ -46962,7 +46965,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47040,7 +47043,7 @@
         <v>0.2</v>
       </c>
       <c r="AP222">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ222">
         <v>0.45</v>
@@ -47374,7 +47377,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47786,7 +47789,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -47992,7 +47995,7 @@
         <v>200</v>
       </c>
       <c r="P227" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q227">
         <v>2.25</v>
@@ -48404,7 +48407,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48485,7 +48488,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ229">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR229">
         <v>1.48</v>
@@ -48610,7 +48613,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48816,7 +48819,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -48894,7 +48897,7 @@
         <v>1.2</v>
       </c>
       <c r="AP231">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AQ231">
         <v>1.36</v>
@@ -49392,7 +49395,7 @@
         <v>233</v>
       </c>
       <c r="B234">
-        <v>7728430</v>
+        <v>7728433</v>
       </c>
       <c r="C234" t="s">
         <v>68</v>
@@ -49407,10 +49410,10 @@
         <v>22</v>
       </c>
       <c r="G234" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H234" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I234">
         <v>1</v>
@@ -49422,175 +49425,999 @@
         <v>1</v>
       </c>
       <c r="L234">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M234">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N234">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O234" t="s">
-        <v>245</v>
+        <v>156</v>
       </c>
       <c r="P234" t="s">
-        <v>336</v>
+        <v>94</v>
       </c>
       <c r="Q234">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="R234">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="S234">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="T234">
+        <v>1.67</v>
+      </c>
+      <c r="U234">
+        <v>2.1</v>
+      </c>
+      <c r="V234">
+        <v>4.33</v>
+      </c>
+      <c r="W234">
+        <v>1.2</v>
+      </c>
+      <c r="X234">
+        <v>15</v>
+      </c>
+      <c r="Y234">
+        <v>1.03</v>
+      </c>
+      <c r="Z234">
+        <v>2.64</v>
+      </c>
+      <c r="AA234">
+        <v>2.9</v>
+      </c>
+      <c r="AB234">
+        <v>3.02</v>
+      </c>
+      <c r="AC234">
+        <v>1.12</v>
+      </c>
+      <c r="AD234">
+        <v>6</v>
+      </c>
+      <c r="AE234">
+        <v>1.6</v>
+      </c>
+      <c r="AF234">
+        <v>2.15</v>
+      </c>
+      <c r="AG234">
+        <v>2.9</v>
+      </c>
+      <c r="AH234">
+        <v>1.36</v>
+      </c>
+      <c r="AI234">
+        <v>2.38</v>
+      </c>
+      <c r="AJ234">
+        <v>1.53</v>
+      </c>
+      <c r="AK234">
+        <v>1.25</v>
+      </c>
+      <c r="AL234">
+        <v>1.33</v>
+      </c>
+      <c r="AM234">
+        <v>1.63</v>
+      </c>
+      <c r="AN234">
+        <v>1.9</v>
+      </c>
+      <c r="AO234">
         <v>1.4</v>
       </c>
-      <c r="U234">
-        <v>2.75</v>
-      </c>
-      <c r="V234">
-        <v>2.75</v>
-      </c>
-      <c r="W234">
-        <v>1.4</v>
-      </c>
-      <c r="X234">
-        <v>8</v>
-      </c>
-      <c r="Y234">
-        <v>1.08</v>
-      </c>
-      <c r="Z234">
-        <v>2.12</v>
-      </c>
-      <c r="AA234">
-        <v>3.44</v>
-      </c>
-      <c r="AB234">
-        <v>3.44</v>
-      </c>
-      <c r="AC234">
-        <v>1.06</v>
-      </c>
-      <c r="AD234">
-        <v>8.5</v>
-      </c>
-      <c r="AE234">
-        <v>1.3</v>
-      </c>
-      <c r="AF234">
-        <v>3.3</v>
-      </c>
-      <c r="AG234">
-        <v>1.94</v>
-      </c>
-      <c r="AH234">
-        <v>1.87</v>
-      </c>
-      <c r="AI234">
-        <v>1.73</v>
-      </c>
-      <c r="AJ234">
-        <v>2</v>
-      </c>
-      <c r="AK234">
-        <v>1.32</v>
-      </c>
-      <c r="AL234">
-        <v>1.31</v>
-      </c>
-      <c r="AM234">
-        <v>1.66</v>
-      </c>
-      <c r="AN234">
-        <v>1.4</v>
-      </c>
-      <c r="AO234">
-        <v>2.2</v>
-      </c>
       <c r="AP234">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AQ234">
-        <v>2.09</v>
+        <v>1.27</v>
       </c>
       <c r="AR234">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AS234">
+        <v>1.14</v>
+      </c>
+      <c r="AT234">
+        <v>2.3</v>
+      </c>
+      <c r="AU234">
+        <v>5</v>
+      </c>
+      <c r="AV234">
+        <v>3</v>
+      </c>
+      <c r="AW234">
+        <v>22</v>
+      </c>
+      <c r="AX234">
+        <v>2</v>
+      </c>
+      <c r="AY234">
+        <v>34</v>
+      </c>
+      <c r="AZ234">
+        <v>5</v>
+      </c>
+      <c r="BA234">
+        <v>16</v>
+      </c>
+      <c r="BB234">
+        <v>2</v>
+      </c>
+      <c r="BC234">
+        <v>18</v>
+      </c>
+      <c r="BD234">
+        <v>1.71</v>
+      </c>
+      <c r="BE234">
+        <v>6.5</v>
+      </c>
+      <c r="BF234">
+        <v>2.4</v>
+      </c>
+      <c r="BG234">
         <v>1.38</v>
       </c>
-      <c r="AT234">
-        <v>2.94</v>
-      </c>
-      <c r="AU234">
-        <v>-1</v>
-      </c>
-      <c r="AV234">
-        <v>-1</v>
-      </c>
-      <c r="AW234">
-        <v>-1</v>
-      </c>
-      <c r="AX234">
-        <v>-1</v>
-      </c>
-      <c r="AY234">
-        <v>-1</v>
-      </c>
-      <c r="AZ234">
-        <v>-1</v>
-      </c>
-      <c r="BA234">
-        <v>-1</v>
-      </c>
-      <c r="BB234">
-        <v>-1</v>
-      </c>
-      <c r="BC234">
-        <v>-1</v>
-      </c>
-      <c r="BD234">
-        <v>1.86</v>
-      </c>
-      <c r="BE234">
-        <v>6.4</v>
-      </c>
-      <c r="BF234">
-        <v>2.15</v>
-      </c>
-      <c r="BG234">
-        <v>1.37</v>
-      </c>
       <c r="BH234">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="BI234">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="BJ234">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BK234">
         <v>2.02</v>
       </c>
       <c r="BL234">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BM234">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="BN234">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BO234">
         <v>3.4</v>
       </c>
       <c r="BP234">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7728430</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45668.51041666666</v>
+      </c>
+      <c r="F235">
+        <v>22</v>
+      </c>
+      <c r="G235" t="s">
+        <v>85</v>
+      </c>
+      <c r="H235" t="s">
+        <v>77</v>
+      </c>
+      <c r="I235">
+        <v>1</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235">
+        <v>1</v>
+      </c>
+      <c r="L235">
+        <v>2</v>
+      </c>
+      <c r="M235">
+        <v>2</v>
+      </c>
+      <c r="N235">
+        <v>4</v>
+      </c>
+      <c r="O235" t="s">
+        <v>245</v>
+      </c>
+      <c r="P235" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q235">
+        <v>2.75</v>
+      </c>
+      <c r="R235">
+        <v>2.2</v>
+      </c>
+      <c r="S235">
+        <v>3.75</v>
+      </c>
+      <c r="T235">
+        <v>1.4</v>
+      </c>
+      <c r="U235">
+        <v>2.75</v>
+      </c>
+      <c r="V235">
+        <v>2.75</v>
+      </c>
+      <c r="W235">
+        <v>1.4</v>
+      </c>
+      <c r="X235">
+        <v>8</v>
+      </c>
+      <c r="Y235">
+        <v>1.08</v>
+      </c>
+      <c r="Z235">
+        <v>2.12</v>
+      </c>
+      <c r="AA235">
+        <v>3.44</v>
+      </c>
+      <c r="AB235">
+        <v>3.44</v>
+      </c>
+      <c r="AC235">
+        <v>1.06</v>
+      </c>
+      <c r="AD235">
+        <v>8.5</v>
+      </c>
+      <c r="AE235">
+        <v>1.3</v>
+      </c>
+      <c r="AF235">
+        <v>3.3</v>
+      </c>
+      <c r="AG235">
+        <v>1.94</v>
+      </c>
+      <c r="AH235">
+        <v>1.87</v>
+      </c>
+      <c r="AI235">
+        <v>1.73</v>
+      </c>
+      <c r="AJ235">
+        <v>2</v>
+      </c>
+      <c r="AK235">
+        <v>1.32</v>
+      </c>
+      <c r="AL235">
+        <v>1.31</v>
+      </c>
+      <c r="AM235">
+        <v>1.66</v>
+      </c>
+      <c r="AN235">
+        <v>1.4</v>
+      </c>
+      <c r="AO235">
+        <v>2.2</v>
+      </c>
+      <c r="AP235">
+        <v>1.36</v>
+      </c>
+      <c r="AQ235">
+        <v>2.09</v>
+      </c>
+      <c r="AR235">
+        <v>1.56</v>
+      </c>
+      <c r="AS235">
+        <v>1.38</v>
+      </c>
+      <c r="AT235">
+        <v>2.94</v>
+      </c>
+      <c r="AU235">
+        <v>4</v>
+      </c>
+      <c r="AV235">
+        <v>11</v>
+      </c>
+      <c r="AW235">
+        <v>7</v>
+      </c>
+      <c r="AX235">
+        <v>10</v>
+      </c>
+      <c r="AY235">
+        <v>11</v>
+      </c>
+      <c r="AZ235">
+        <v>22</v>
+      </c>
+      <c r="BA235">
+        <v>4</v>
+      </c>
+      <c r="BB235">
+        <v>5</v>
+      </c>
+      <c r="BC235">
+        <v>9</v>
+      </c>
+      <c r="BD235">
+        <v>1.86</v>
+      </c>
+      <c r="BE235">
+        <v>6.4</v>
+      </c>
+      <c r="BF235">
+        <v>2.15</v>
+      </c>
+      <c r="BG235">
+        <v>1.37</v>
+      </c>
+      <c r="BH235">
+        <v>2.75</v>
+      </c>
+      <c r="BI235">
+        <v>1.63</v>
+      </c>
+      <c r="BJ235">
+        <v>2.08</v>
+      </c>
+      <c r="BK235">
+        <v>2.02</v>
+      </c>
+      <c r="BL235">
+        <v>1.67</v>
+      </c>
+      <c r="BM235">
+        <v>2.55</v>
+      </c>
+      <c r="BN235">
+        <v>1.43</v>
+      </c>
+      <c r="BO235">
+        <v>3.4</v>
+      </c>
+      <c r="BP235">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7728438</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45668.60416666666</v>
+      </c>
+      <c r="F236">
+        <v>22</v>
+      </c>
+      <c r="G236" t="s">
+        <v>84</v>
+      </c>
+      <c r="H236" t="s">
+        <v>86</v>
+      </c>
+      <c r="I236">
+        <v>1</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>1</v>
+      </c>
+      <c r="L236">
+        <v>2</v>
+      </c>
+      <c r="M236">
+        <v>0</v>
+      </c>
+      <c r="N236">
+        <v>2</v>
+      </c>
+      <c r="O236" t="s">
+        <v>246</v>
+      </c>
+      <c r="P236" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q236">
+        <v>3.2</v>
+      </c>
+      <c r="R236">
+        <v>2</v>
+      </c>
+      <c r="S236">
+        <v>3.75</v>
+      </c>
+      <c r="T236">
+        <v>1.5</v>
+      </c>
+      <c r="U236">
+        <v>2.5</v>
+      </c>
+      <c r="V236">
+        <v>3.4</v>
+      </c>
+      <c r="W236">
+        <v>1.3</v>
+      </c>
+      <c r="X236">
+        <v>10</v>
+      </c>
+      <c r="Y236">
+        <v>1.06</v>
+      </c>
+      <c r="Z236">
+        <v>3.12</v>
+      </c>
+      <c r="AA236">
+        <v>3.18</v>
+      </c>
+      <c r="AB236">
+        <v>2.38</v>
+      </c>
+      <c r="AC236">
+        <v>1.07</v>
+      </c>
+      <c r="AD236">
+        <v>8</v>
+      </c>
+      <c r="AE236">
+        <v>1.36</v>
+      </c>
+      <c r="AF236">
+        <v>3</v>
+      </c>
+      <c r="AG236">
+        <v>2</v>
+      </c>
+      <c r="AH236">
+        <v>1.82</v>
+      </c>
+      <c r="AI236">
+        <v>1.91</v>
+      </c>
+      <c r="AJ236">
+        <v>1.8</v>
+      </c>
+      <c r="AK236">
+        <v>1.38</v>
+      </c>
+      <c r="AL236">
+        <v>1.33</v>
+      </c>
+      <c r="AM236">
+        <v>1.53</v>
+      </c>
+      <c r="AN236">
+        <v>1</v>
+      </c>
+      <c r="AO236">
+        <v>1.5</v>
+      </c>
+      <c r="AP236">
+        <v>1.2</v>
+      </c>
+      <c r="AQ236">
+        <v>1.36</v>
+      </c>
+      <c r="AR236">
+        <v>1.23</v>
+      </c>
+      <c r="AS236">
+        <v>1.34</v>
+      </c>
+      <c r="AT236">
+        <v>2.57</v>
+      </c>
+      <c r="AU236">
+        <v>5</v>
+      </c>
+      <c r="AV236">
+        <v>2</v>
+      </c>
+      <c r="AW236">
+        <v>5</v>
+      </c>
+      <c r="AX236">
+        <v>5</v>
+      </c>
+      <c r="AY236">
+        <v>12</v>
+      </c>
+      <c r="AZ236">
+        <v>9</v>
+      </c>
+      <c r="BA236">
+        <v>1</v>
+      </c>
+      <c r="BB236">
+        <v>9</v>
+      </c>
+      <c r="BC236">
+        <v>10</v>
+      </c>
+      <c r="BD236">
+        <v>1.9</v>
+      </c>
+      <c r="BE236">
+        <v>6.25</v>
+      </c>
+      <c r="BF236">
+        <v>2.1</v>
+      </c>
+      <c r="BG236">
+        <v>1.36</v>
+      </c>
+      <c r="BH236">
+        <v>2.8</v>
+      </c>
+      <c r="BI236">
+        <v>1.6</v>
+      </c>
+      <c r="BJ236">
+        <v>2.14</v>
+      </c>
+      <c r="BK236">
+        <v>1.98</v>
+      </c>
+      <c r="BL236">
+        <v>1.71</v>
+      </c>
+      <c r="BM236">
+        <v>2.55</v>
+      </c>
+      <c r="BN236">
+        <v>1.43</v>
+      </c>
+      <c r="BO236">
+        <v>3.3</v>
+      </c>
+      <c r="BP236">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7728439</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45668.60416666666</v>
+      </c>
+      <c r="F237">
+        <v>22</v>
+      </c>
+      <c r="G237" t="s">
+        <v>83</v>
+      </c>
+      <c r="H237" t="s">
+        <v>75</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237">
+        <v>1</v>
+      </c>
+      <c r="M237">
+        <v>1</v>
+      </c>
+      <c r="N237">
+        <v>2</v>
+      </c>
+      <c r="O237" t="s">
+        <v>224</v>
+      </c>
+      <c r="P237" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q237">
+        <v>3.2</v>
+      </c>
+      <c r="R237">
+        <v>2.05</v>
+      </c>
+      <c r="S237">
+        <v>3.6</v>
+      </c>
+      <c r="T237">
+        <v>1.44</v>
+      </c>
+      <c r="U237">
+        <v>2.63</v>
+      </c>
+      <c r="V237">
+        <v>3.25</v>
+      </c>
+      <c r="W237">
+        <v>1.33</v>
+      </c>
+      <c r="X237">
+        <v>10</v>
+      </c>
+      <c r="Y237">
+        <v>1.06</v>
+      </c>
+      <c r="Z237">
+        <v>2.56</v>
+      </c>
+      <c r="AA237">
+        <v>3.12</v>
+      </c>
+      <c r="AB237">
+        <v>2.9</v>
+      </c>
+      <c r="AC237">
+        <v>1.07</v>
+      </c>
+      <c r="AD237">
+        <v>8</v>
+      </c>
+      <c r="AE237">
+        <v>1.33</v>
+      </c>
+      <c r="AF237">
+        <v>3.1</v>
+      </c>
+      <c r="AG237">
+        <v>2.15</v>
+      </c>
+      <c r="AH237">
+        <v>1.61</v>
+      </c>
+      <c r="AI237">
+        <v>1.83</v>
+      </c>
+      <c r="AJ237">
+        <v>1.83</v>
+      </c>
+      <c r="AK237">
+        <v>1.4</v>
+      </c>
+      <c r="AL237">
+        <v>1.33</v>
+      </c>
+      <c r="AM237">
+        <v>1.51</v>
+      </c>
+      <c r="AN237">
+        <v>1.9</v>
+      </c>
+      <c r="AO237">
+        <v>1.22</v>
+      </c>
+      <c r="AP237">
+        <v>1.82</v>
+      </c>
+      <c r="AQ237">
+        <v>1.2</v>
+      </c>
+      <c r="AR237">
+        <v>1.37</v>
+      </c>
+      <c r="AS237">
+        <v>1.43</v>
+      </c>
+      <c r="AT237">
+        <v>2.8</v>
+      </c>
+      <c r="AU237">
+        <v>2</v>
+      </c>
+      <c r="AV237">
+        <v>5</v>
+      </c>
+      <c r="AW237">
+        <v>10</v>
+      </c>
+      <c r="AX237">
+        <v>8</v>
+      </c>
+      <c r="AY237">
+        <v>16</v>
+      </c>
+      <c r="AZ237">
+        <v>17</v>
+      </c>
+      <c r="BA237">
+        <v>5</v>
+      </c>
+      <c r="BB237">
+        <v>4</v>
+      </c>
+      <c r="BC237">
+        <v>9</v>
+      </c>
+      <c r="BD237">
+        <v>1.73</v>
+      </c>
+      <c r="BE237">
+        <v>6.5</v>
+      </c>
+      <c r="BF237">
+        <v>2.33</v>
+      </c>
+      <c r="BG237">
+        <v>1.29</v>
+      </c>
+      <c r="BH237">
+        <v>3.15</v>
+      </c>
+      <c r="BI237">
+        <v>1.5</v>
+      </c>
+      <c r="BJ237">
+        <v>2.35</v>
+      </c>
+      <c r="BK237">
+        <v>1.83</v>
+      </c>
+      <c r="BL237">
+        <v>1.83</v>
+      </c>
+      <c r="BM237">
+        <v>2.28</v>
+      </c>
+      <c r="BN237">
+        <v>1.53</v>
+      </c>
+      <c r="BO237">
+        <v>2.95</v>
+      </c>
+      <c r="BP237">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7728434</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45668.70833333334</v>
+      </c>
+      <c r="F238">
+        <v>22</v>
+      </c>
+      <c r="G238" t="s">
+        <v>89</v>
+      </c>
+      <c r="H238" t="s">
+        <v>76</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>0</v>
+      </c>
+      <c r="L238">
+        <v>1</v>
+      </c>
+      <c r="M238">
+        <v>1</v>
+      </c>
+      <c r="N238">
+        <v>2</v>
+      </c>
+      <c r="O238" t="s">
+        <v>236</v>
+      </c>
+      <c r="P238" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q238">
+        <v>2.88</v>
+      </c>
+      <c r="R238">
+        <v>1.95</v>
+      </c>
+      <c r="S238">
+        <v>4.5</v>
+      </c>
+      <c r="T238">
+        <v>1.57</v>
+      </c>
+      <c r="U238">
+        <v>2.25</v>
+      </c>
+      <c r="V238">
+        <v>3.75</v>
+      </c>
+      <c r="W238">
+        <v>1.25</v>
+      </c>
+      <c r="X238">
+        <v>11</v>
+      </c>
+      <c r="Y238">
+        <v>1.05</v>
+      </c>
+      <c r="Z238">
+        <v>2.08</v>
+      </c>
+      <c r="AA238">
+        <v>3.04</v>
+      </c>
+      <c r="AB238">
+        <v>3.92</v>
+      </c>
+      <c r="AC238">
+        <v>1.1</v>
+      </c>
+      <c r="AD238">
+        <v>7</v>
+      </c>
+      <c r="AE238">
+        <v>1.45</v>
+      </c>
+      <c r="AF238">
+        <v>2.6</v>
+      </c>
+      <c r="AG238">
+        <v>2.3</v>
+      </c>
+      <c r="AH238">
+        <v>1.53</v>
+      </c>
+      <c r="AI238">
+        <v>2.1</v>
+      </c>
+      <c r="AJ238">
+        <v>1.67</v>
+      </c>
+      <c r="AK238">
+        <v>1.27</v>
+      </c>
+      <c r="AL238">
+        <v>1.35</v>
+      </c>
+      <c r="AM238">
+        <v>1.68</v>
+      </c>
+      <c r="AN238">
+        <v>2.1</v>
+      </c>
+      <c r="AO238">
+        <v>1.1</v>
+      </c>
+      <c r="AP238">
+        <v>2</v>
+      </c>
+      <c r="AQ238">
+        <v>1.09</v>
+      </c>
+      <c r="AR238">
+        <v>1.62</v>
+      </c>
+      <c r="AS238">
+        <v>1.22</v>
+      </c>
+      <c r="AT238">
+        <v>2.84</v>
+      </c>
+      <c r="AU238">
+        <v>5</v>
+      </c>
+      <c r="AV238">
+        <v>3</v>
+      </c>
+      <c r="AW238">
+        <v>6</v>
+      </c>
+      <c r="AX238">
+        <v>6</v>
+      </c>
+      <c r="AY238">
+        <v>13</v>
+      </c>
+      <c r="AZ238">
+        <v>10</v>
+      </c>
+      <c r="BA238">
+        <v>4</v>
+      </c>
+      <c r="BB238">
+        <v>4</v>
+      </c>
+      <c r="BC238">
+        <v>8</v>
+      </c>
+      <c r="BD238">
+        <v>1.63</v>
+      </c>
+      <c r="BE238">
+        <v>6.75</v>
+      </c>
+      <c r="BF238">
+        <v>2.55</v>
+      </c>
+      <c r="BG238">
+        <v>1.34</v>
+      </c>
+      <c r="BH238">
+        <v>2.88</v>
+      </c>
+      <c r="BI238">
+        <v>1.58</v>
+      </c>
+      <c r="BJ238">
+        <v>2.16</v>
+      </c>
+      <c r="BK238">
+        <v>1.95</v>
+      </c>
+      <c r="BL238">
+        <v>1.72</v>
+      </c>
+      <c r="BM238">
+        <v>2.5</v>
+      </c>
+      <c r="BN238">
+        <v>1.44</v>
+      </c>
+      <c r="BO238">
+        <v>3.3</v>
+      </c>
+      <c r="BP238">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="339">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1029,6 +1029,9 @@
   <si>
     <t>['71', '76']</t>
   </si>
+  <si>
+    <t>['31', '51', '69']</t>
+  </si>
 </sst>
 </file>
 
@@ -1389,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP238"/>
+  <dimension ref="A1:BP241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2135,10 +2138,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ4">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2962,7 +2965,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3168,7 +3171,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ9">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3577,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ11">
         <v>1.27</v>
@@ -5228,7 +5231,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ19">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR19">
         <v>0</v>
@@ -5846,7 +5849,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ22">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6049,7 +6052,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ23">
         <v>0.82</v>
@@ -6667,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ26">
         <v>0.18</v>
@@ -7700,7 +7703,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ31">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR31">
         <v>0.48</v>
@@ -8112,7 +8115,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ33">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR33">
         <v>0.95</v>
@@ -8315,7 +8318,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ34">
         <v>0.45</v>
@@ -9345,7 +9348,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ39">
         <v>1</v>
@@ -9760,7 +9763,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ41">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR41">
         <v>1</v>
@@ -9966,7 +9969,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ42">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR42">
         <v>1.8</v>
@@ -10787,7 +10790,7 @@
         <v>0.5</v>
       </c>
       <c r="AP46">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ46">
         <v>1.2</v>
@@ -12232,7 +12235,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ53">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR53">
         <v>1.46</v>
@@ -12435,7 +12438,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ54">
         <v>1</v>
@@ -12641,7 +12644,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ55">
         <v>1.5</v>
@@ -13880,7 +13883,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ61">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR61">
         <v>1.87</v>
@@ -14701,7 +14704,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ65">
         <v>1.27</v>
@@ -15525,7 +15528,7 @@
         <v>0.5</v>
       </c>
       <c r="AP69">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ69">
         <v>0.55</v>
@@ -15940,7 +15943,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ71">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR71">
         <v>1.44</v>
@@ -16352,7 +16355,7 @@
         <v>2</v>
       </c>
       <c r="AQ73">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR73">
         <v>2.06</v>
@@ -16967,7 +16970,7 @@
         <v>0.5</v>
       </c>
       <c r="AP76">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -19854,7 +19857,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ90">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR90">
         <v>1.45</v>
@@ -20263,7 +20266,7 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -20884,7 +20887,7 @@
         <v>2</v>
       </c>
       <c r="AQ95">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR95">
         <v>1.44</v>
@@ -21090,7 +21093,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ96">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR96">
         <v>1.53</v>
@@ -21705,7 +21708,7 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ99">
         <v>1.2</v>
@@ -22117,7 +22120,7 @@
         <v>1.2</v>
       </c>
       <c r="AP101">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ101">
         <v>0.58</v>
@@ -22944,7 +22947,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ105">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR105">
         <v>1.64</v>
@@ -23353,7 +23356,7 @@
         <v>3</v>
       </c>
       <c r="AP107">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ107">
         <v>2.09</v>
@@ -23765,7 +23768,7 @@
         <v>1.25</v>
       </c>
       <c r="AP109">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ109">
         <v>1.09</v>
@@ -23974,7 +23977,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ110">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR110">
         <v>1.96</v>
@@ -25004,7 +25007,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ115">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR115">
         <v>1.49</v>
@@ -26649,7 +26652,7 @@
         <v>1.17</v>
       </c>
       <c r="AP123">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ123">
         <v>1.27</v>
@@ -27061,7 +27064,7 @@
         <v>1</v>
       </c>
       <c r="AP125">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ125">
         <v>0.55</v>
@@ -27885,7 +27888,7 @@
         <v>1.4</v>
       </c>
       <c r="AP129">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ129">
         <v>0.82</v>
@@ -28300,7 +28303,7 @@
         <v>2</v>
       </c>
       <c r="AQ131">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR131">
         <v>1.16</v>
@@ -28506,7 +28509,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ132">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR132">
         <v>1.78</v>
@@ -30357,10 +30360,10 @@
         <v>1.14</v>
       </c>
       <c r="AP141">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ141">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR141">
         <v>1.42</v>
@@ -30772,7 +30775,7 @@
         <v>2</v>
       </c>
       <c r="AQ143">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR143">
         <v>1.11</v>
@@ -31387,7 +31390,7 @@
         <v>2</v>
       </c>
       <c r="AP146">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ146">
         <v>1.36</v>
@@ -33653,7 +33656,7 @@
         <v>0.17</v>
       </c>
       <c r="AP157">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ157">
         <v>0.45</v>
@@ -34892,7 +34895,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ163">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR163">
         <v>1.14</v>
@@ -35098,7 +35101,7 @@
         <v>0.8</v>
       </c>
       <c r="AQ164">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR164">
         <v>1.2</v>
@@ -35713,10 +35716,10 @@
         <v>1.75</v>
       </c>
       <c r="AP167">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ167">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR167">
         <v>1.65</v>
@@ -36949,7 +36952,7 @@
         <v>1</v>
       </c>
       <c r="AP173">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ173">
         <v>1.27</v>
@@ -38391,7 +38394,7 @@
         <v>1</v>
       </c>
       <c r="AP180">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ180">
         <v>1.2</v>
@@ -40042,7 +40045,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ188">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR188">
         <v>1.17</v>
@@ -40245,7 +40248,7 @@
         <v>1.13</v>
       </c>
       <c r="AP189">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ189">
         <v>1</v>
@@ -40660,7 +40663,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ191">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR191">
         <v>1.48</v>
@@ -41278,7 +41281,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ194">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR194">
         <v>1.4</v>
@@ -41893,7 +41896,7 @@
         <v>0.25</v>
       </c>
       <c r="AP197">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ197">
         <v>0.18</v>
@@ -42717,7 +42720,7 @@
         <v>1.22</v>
       </c>
       <c r="AP201">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ201">
         <v>1.09</v>
@@ -43132,7 +43135,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ203">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR203">
         <v>1.49</v>
@@ -44574,7 +44577,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ210">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR210">
         <v>1.59</v>
@@ -44777,7 +44780,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP211">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ211">
         <v>0.5</v>
@@ -45192,7 +45195,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ213">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR213">
         <v>1.08</v>
@@ -45807,7 +45810,7 @@
         <v>0.78</v>
       </c>
       <c r="AP216">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AQ216">
         <v>0.82</v>
@@ -46013,7 +46016,7 @@
         <v>2.44</v>
       </c>
       <c r="AP217">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ217">
         <v>2.09</v>
@@ -48900,7 +48903,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ231">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AR231">
         <v>1.26</v>
@@ -49118,22 +49121,22 @@
         <v>2.95</v>
       </c>
       <c r="AU232">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV232">
+        <v>4</v>
+      </c>
+      <c r="AW232">
+        <v>8</v>
+      </c>
+      <c r="AX232">
         <v>3</v>
       </c>
-      <c r="AW232">
-        <v>12</v>
-      </c>
-      <c r="AX232">
-        <v>7</v>
-      </c>
       <c r="AY232">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ232">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA232">
         <v>5</v>
@@ -49330,16 +49333,16 @@
         <v>3</v>
       </c>
       <c r="AW233">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY233">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AZ233">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA233">
         <v>8</v>
@@ -49530,19 +49533,19 @@
         <v>2.3</v>
       </c>
       <c r="AU234">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV234">
         <v>3</v>
       </c>
       <c r="AW234">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AX234">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY234">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AZ234">
         <v>5</v>
@@ -49739,19 +49742,19 @@
         <v>4</v>
       </c>
       <c r="AV235">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW235">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX235">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AY235">
         <v>11</v>
       </c>
       <c r="AZ235">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BA235">
         <v>4</v>
@@ -49942,22 +49945,22 @@
         <v>2.57</v>
       </c>
       <c r="AU236">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV236">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW236">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX236">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY236">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ236">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA236">
         <v>1</v>
@@ -50154,16 +50157,16 @@
         <v>5</v>
       </c>
       <c r="AW237">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AX237">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AY237">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ237">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA237">
         <v>5</v>
@@ -50360,16 +50363,16 @@
         <v>3</v>
       </c>
       <c r="AW238">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AX238">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY238">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ238">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA238">
         <v>4</v>
@@ -50417,6 +50420,624 @@
         <v>3.3</v>
       </c>
       <c r="BP238">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7728435</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45669.41666666666</v>
+      </c>
+      <c r="F239">
+        <v>22</v>
+      </c>
+      <c r="G239" t="s">
+        <v>88</v>
+      </c>
+      <c r="H239" t="s">
+        <v>90</v>
+      </c>
+      <c r="I239">
+        <v>0</v>
+      </c>
+      <c r="J239">
+        <v>1</v>
+      </c>
+      <c r="K239">
+        <v>1</v>
+      </c>
+      <c r="L239">
+        <v>0</v>
+      </c>
+      <c r="M239">
+        <v>3</v>
+      </c>
+      <c r="N239">
+        <v>3</v>
+      </c>
+      <c r="O239" t="s">
+        <v>94</v>
+      </c>
+      <c r="P239" t="s">
+        <v>338</v>
+      </c>
+      <c r="Q239">
+        <v>3.2</v>
+      </c>
+      <c r="R239">
+        <v>2.25</v>
+      </c>
+      <c r="S239">
+        <v>3.1</v>
+      </c>
+      <c r="T239">
+        <v>1.36</v>
+      </c>
+      <c r="U239">
+        <v>3</v>
+      </c>
+      <c r="V239">
+        <v>2.63</v>
+      </c>
+      <c r="W239">
+        <v>1.44</v>
+      </c>
+      <c r="X239">
+        <v>7</v>
+      </c>
+      <c r="Y239">
+        <v>1.1</v>
+      </c>
+      <c r="Z239">
+        <v>2.45</v>
+      </c>
+      <c r="AA239">
+        <v>3.2</v>
+      </c>
+      <c r="AB239">
+        <v>2.5</v>
+      </c>
+      <c r="AC239">
+        <v>1.05</v>
+      </c>
+      <c r="AD239">
+        <v>9.5</v>
+      </c>
+      <c r="AE239">
+        <v>1.22</v>
+      </c>
+      <c r="AF239">
+        <v>4</v>
+      </c>
+      <c r="AG239">
+        <v>1.7</v>
+      </c>
+      <c r="AH239">
+        <v>2</v>
+      </c>
+      <c r="AI239">
+        <v>1.62</v>
+      </c>
+      <c r="AJ239">
+        <v>2.2</v>
+      </c>
+      <c r="AK239">
+        <v>1.49</v>
+      </c>
+      <c r="AL239">
+        <v>1.3</v>
+      </c>
+      <c r="AM239">
+        <v>1.46</v>
+      </c>
+      <c r="AN239">
+        <v>2.2</v>
+      </c>
+      <c r="AO239">
+        <v>1.64</v>
+      </c>
+      <c r="AP239">
+        <v>2</v>
+      </c>
+      <c r="AQ239">
+        <v>1.75</v>
+      </c>
+      <c r="AR239">
+        <v>1.67</v>
+      </c>
+      <c r="AS239">
+        <v>1.48</v>
+      </c>
+      <c r="AT239">
+        <v>3.15</v>
+      </c>
+      <c r="AU239">
+        <v>4</v>
+      </c>
+      <c r="AV239">
+        <v>6</v>
+      </c>
+      <c r="AW239">
+        <v>2</v>
+      </c>
+      <c r="AX239">
+        <v>7</v>
+      </c>
+      <c r="AY239">
+        <v>8</v>
+      </c>
+      <c r="AZ239">
+        <v>15</v>
+      </c>
+      <c r="BA239">
+        <v>6</v>
+      </c>
+      <c r="BB239">
+        <v>2</v>
+      </c>
+      <c r="BC239">
+        <v>8</v>
+      </c>
+      <c r="BD239">
+        <v>1.76</v>
+      </c>
+      <c r="BE239">
+        <v>6.4</v>
+      </c>
+      <c r="BF239">
+        <v>2.28</v>
+      </c>
+      <c r="BG239">
+        <v>1.3</v>
+      </c>
+      <c r="BH239">
+        <v>3.05</v>
+      </c>
+      <c r="BI239">
+        <v>1.52</v>
+      </c>
+      <c r="BJ239">
+        <v>2.28</v>
+      </c>
+      <c r="BK239">
+        <v>1.85</v>
+      </c>
+      <c r="BL239">
+        <v>1.81</v>
+      </c>
+      <c r="BM239">
+        <v>2.35</v>
+      </c>
+      <c r="BN239">
+        <v>1.5</v>
+      </c>
+      <c r="BO239">
+        <v>3.05</v>
+      </c>
+      <c r="BP239">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7728431</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45669.51041666666</v>
+      </c>
+      <c r="F240">
+        <v>22</v>
+      </c>
+      <c r="G240" t="s">
+        <v>72</v>
+      </c>
+      <c r="H240" t="s">
+        <v>82</v>
+      </c>
+      <c r="I240">
+        <v>0</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240">
+        <v>0</v>
+      </c>
+      <c r="L240">
+        <v>0</v>
+      </c>
+      <c r="M240">
+        <v>0</v>
+      </c>
+      <c r="N240">
+        <v>0</v>
+      </c>
+      <c r="O240" t="s">
+        <v>94</v>
+      </c>
+      <c r="P240" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q240">
+        <v>3.2</v>
+      </c>
+      <c r="R240">
+        <v>2.05</v>
+      </c>
+      <c r="S240">
+        <v>3.6</v>
+      </c>
+      <c r="T240">
+        <v>1.44</v>
+      </c>
+      <c r="U240">
+        <v>2.63</v>
+      </c>
+      <c r="V240">
+        <v>3.4</v>
+      </c>
+      <c r="W240">
+        <v>1.3</v>
+      </c>
+      <c r="X240">
+        <v>10</v>
+      </c>
+      <c r="Y240">
+        <v>1.06</v>
+      </c>
+      <c r="Z240">
+        <v>2.3</v>
+      </c>
+      <c r="AA240">
+        <v>3.1</v>
+      </c>
+      <c r="AB240">
+        <v>3</v>
+      </c>
+      <c r="AC240">
+        <v>1.08</v>
+      </c>
+      <c r="AD240">
+        <v>7.5</v>
+      </c>
+      <c r="AE240">
+        <v>1.36</v>
+      </c>
+      <c r="AF240">
+        <v>2.95</v>
+      </c>
+      <c r="AG240">
+        <v>2.2</v>
+      </c>
+      <c r="AH240">
+        <v>1.53</v>
+      </c>
+      <c r="AI240">
+        <v>1.83</v>
+      </c>
+      <c r="AJ240">
+        <v>1.83</v>
+      </c>
+      <c r="AK240">
+        <v>1.38</v>
+      </c>
+      <c r="AL240">
+        <v>1.34</v>
+      </c>
+      <c r="AM240">
+        <v>1.53</v>
+      </c>
+      <c r="AN240">
+        <v>1.18</v>
+      </c>
+      <c r="AO240">
+        <v>1.36</v>
+      </c>
+      <c r="AP240">
+        <v>1.17</v>
+      </c>
+      <c r="AQ240">
+        <v>1.33</v>
+      </c>
+      <c r="AR240">
+        <v>1.44</v>
+      </c>
+      <c r="AS240">
+        <v>1.27</v>
+      </c>
+      <c r="AT240">
+        <v>2.71</v>
+      </c>
+      <c r="AU240">
+        <v>4</v>
+      </c>
+      <c r="AV240">
+        <v>2</v>
+      </c>
+      <c r="AW240">
+        <v>5</v>
+      </c>
+      <c r="AX240">
+        <v>9</v>
+      </c>
+      <c r="AY240">
+        <v>11</v>
+      </c>
+      <c r="AZ240">
+        <v>14</v>
+      </c>
+      <c r="BA240">
+        <v>2</v>
+      </c>
+      <c r="BB240">
+        <v>2</v>
+      </c>
+      <c r="BC240">
+        <v>4</v>
+      </c>
+      <c r="BD240">
+        <v>1.84</v>
+      </c>
+      <c r="BE240">
+        <v>6.4</v>
+      </c>
+      <c r="BF240">
+        <v>2.17</v>
+      </c>
+      <c r="BG240">
+        <v>1.37</v>
+      </c>
+      <c r="BH240">
+        <v>2.8</v>
+      </c>
+      <c r="BI240">
+        <v>1.63</v>
+      </c>
+      <c r="BJ240">
+        <v>2.1</v>
+      </c>
+      <c r="BK240">
+        <v>2.02</v>
+      </c>
+      <c r="BL240">
+        <v>1.67</v>
+      </c>
+      <c r="BM240">
+        <v>2.6</v>
+      </c>
+      <c r="BN240">
+        <v>1.41</v>
+      </c>
+      <c r="BO240">
+        <v>3.4</v>
+      </c>
+      <c r="BP240">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7728432</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45669.51041666666</v>
+      </c>
+      <c r="F241">
+        <v>22</v>
+      </c>
+      <c r="G241" t="s">
+        <v>79</v>
+      </c>
+      <c r="H241" t="s">
+        <v>91</v>
+      </c>
+      <c r="I241">
+        <v>0</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241">
+        <v>0</v>
+      </c>
+      <c r="L241">
+        <v>1</v>
+      </c>
+      <c r="M241">
+        <v>0</v>
+      </c>
+      <c r="N241">
+        <v>1</v>
+      </c>
+      <c r="O241" t="s">
+        <v>119</v>
+      </c>
+      <c r="P241" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q241">
+        <v>2.6</v>
+      </c>
+      <c r="R241">
+        <v>2</v>
+      </c>
+      <c r="S241">
+        <v>5</v>
+      </c>
+      <c r="T241">
+        <v>1.53</v>
+      </c>
+      <c r="U241">
+        <v>2.38</v>
+      </c>
+      <c r="V241">
+        <v>3.5</v>
+      </c>
+      <c r="W241">
+        <v>1.29</v>
+      </c>
+      <c r="X241">
+        <v>11</v>
+      </c>
+      <c r="Y241">
+        <v>1.05</v>
+      </c>
+      <c r="Z241">
+        <v>1.8</v>
+      </c>
+      <c r="AA241">
+        <v>3.1</v>
+      </c>
+      <c r="AB241">
+        <v>4.6</v>
+      </c>
+      <c r="AC241">
+        <v>1.08</v>
+      </c>
+      <c r="AD241">
+        <v>7.5</v>
+      </c>
+      <c r="AE241">
+        <v>1.44</v>
+      </c>
+      <c r="AF241">
+        <v>2.65</v>
+      </c>
+      <c r="AG241">
+        <v>2.3</v>
+      </c>
+      <c r="AH241">
+        <v>1.5</v>
+      </c>
+      <c r="AI241">
+        <v>2.2</v>
+      </c>
+      <c r="AJ241">
+        <v>1.62</v>
+      </c>
+      <c r="AK241">
+        <v>1.19</v>
+      </c>
+      <c r="AL241">
+        <v>1.32</v>
+      </c>
+      <c r="AM241">
+        <v>1.9</v>
+      </c>
+      <c r="AN241">
+        <v>2.09</v>
+      </c>
+      <c r="AO241">
+        <v>1.45</v>
+      </c>
+      <c r="AP241">
+        <v>2.17</v>
+      </c>
+      <c r="AQ241">
+        <v>1.33</v>
+      </c>
+      <c r="AR241">
+        <v>1.63</v>
+      </c>
+      <c r="AS241">
+        <v>1.36</v>
+      </c>
+      <c r="AT241">
+        <v>2.99</v>
+      </c>
+      <c r="AU241">
+        <v>6</v>
+      </c>
+      <c r="AV241">
+        <v>2</v>
+      </c>
+      <c r="AW241">
+        <v>5</v>
+      </c>
+      <c r="AX241">
+        <v>5</v>
+      </c>
+      <c r="AY241">
+        <v>13</v>
+      </c>
+      <c r="AZ241">
+        <v>9</v>
+      </c>
+      <c r="BA241">
+        <v>7</v>
+      </c>
+      <c r="BB241">
+        <v>0</v>
+      </c>
+      <c r="BC241">
+        <v>7</v>
+      </c>
+      <c r="BD241">
+        <v>1.49</v>
+      </c>
+      <c r="BE241">
+        <v>6.75</v>
+      </c>
+      <c r="BF241">
+        <v>2.9</v>
+      </c>
+      <c r="BG241">
+        <v>1.36</v>
+      </c>
+      <c r="BH241">
+        <v>2.8</v>
+      </c>
+      <c r="BI241">
+        <v>1.61</v>
+      </c>
+      <c r="BJ241">
+        <v>2.12</v>
+      </c>
+      <c r="BK241">
+        <v>1.98</v>
+      </c>
+      <c r="BL241">
+        <v>1.7</v>
+      </c>
+      <c r="BM241">
+        <v>2.55</v>
+      </c>
+      <c r="BN241">
+        <v>1.43</v>
+      </c>
+      <c r="BO241">
+        <v>3.3</v>
+      </c>
+      <c r="BP241">
         <v>1.27</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="340">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -757,6 +757,9 @@
     <t>['35', '60']</t>
   </si>
   <si>
+    <t>['13']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -922,9 +925,6 @@
     <t>['18', '31']</t>
   </si>
   <si>
-    <t>['13']</t>
-  </si>
-  <si>
     <t>['41', '45']</t>
   </si>
   <si>
@@ -1031,6 +1031,9 @@
   </si>
   <si>
     <t>['31', '51', '69']</t>
+  </si>
+  <si>
+    <t>['58', '62', '90+6']</t>
   </si>
 </sst>
 </file>
@@ -1392,7 +1395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP241"/>
+  <dimension ref="A1:BP242"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1648,7 +1651,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2060,7 +2063,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2678,7 +2681,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2884,7 +2887,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3090,7 +3093,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3786,7 +3789,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ12">
         <v>0.18</v>
@@ -3914,7 +3917,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -3995,7 +3998,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ13">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR13">
         <v>1.32</v>
@@ -4120,7 +4123,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -5150,7 +5153,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5768,7 +5771,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5974,7 +5977,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6180,7 +6183,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6386,7 +6389,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6592,7 +6595,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6798,7 +6801,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7210,7 +7213,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7828,7 +7831,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -7906,7 +7909,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ32">
         <v>0.58</v>
@@ -8034,7 +8037,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8446,7 +8449,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -9064,7 +9067,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9966,7 +9969,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ42">
         <v>1.75</v>
@@ -10300,7 +10303,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10587,7 +10590,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ45">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR45">
         <v>0.96</v>
@@ -10918,7 +10921,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -12566,7 +12569,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12772,7 +12775,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -12978,7 +12981,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13184,7 +13187,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13468,7 +13471,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ59">
         <v>1.27</v>
@@ -13596,7 +13599,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14214,7 +14217,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14832,7 +14835,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -14913,7 +14916,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ66">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR66">
         <v>1.93</v>
@@ -15244,7 +15247,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15450,7 +15453,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16068,7 +16071,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16274,7 +16277,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16480,7 +16483,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17179,7 +17182,7 @@
         <v>2</v>
       </c>
       <c r="AQ77">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR77">
         <v>1.33</v>
@@ -17304,7 +17307,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17510,7 +17513,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17922,7 +17925,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18128,7 +18131,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18334,7 +18337,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19158,7 +19161,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19236,7 +19239,7 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ87">
         <v>1.36</v>
@@ -19570,7 +19573,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19776,7 +19779,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20188,7 +20191,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20600,7 +20603,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20806,7 +20809,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21836,7 +21839,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23153,7 +23156,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ106">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR106">
         <v>1.12</v>
@@ -23278,7 +23281,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23896,7 +23899,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24308,7 +24311,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24514,7 +24517,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24926,7 +24929,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25004,7 +25007,7 @@
         <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ115">
         <v>1.33</v>
@@ -25750,7 +25753,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26368,7 +26371,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26780,7 +26783,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27192,7 +27195,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27479,7 +27482,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ127">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR127">
         <v>1.1</v>
@@ -27604,7 +27607,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28016,7 +28019,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28222,7 +28225,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28428,7 +28431,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28634,7 +28637,7 @@
         <v>106</v>
       </c>
       <c r="P133" t="s">
-        <v>302</v>
+        <v>247</v>
       </c>
       <c r="Q133">
         <v>3.1</v>
@@ -30694,7 +30697,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -32217,7 +32220,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ150">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR150">
         <v>1.6</v>
@@ -32626,7 +32629,7 @@
         <v>1.14</v>
       </c>
       <c r="AP152">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ152">
         <v>1.09</v>
@@ -33372,7 +33375,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -34686,7 +34689,7 @@
         <v>1</v>
       </c>
       <c r="AP162">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ162">
         <v>1.27</v>
@@ -35513,7 +35516,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ166">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR166">
         <v>1.42</v>
@@ -38110,7 +38113,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -39424,7 +39427,7 @@
         <v>0.86</v>
       </c>
       <c r="AP185">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ185">
         <v>1</v>
@@ -39964,7 +39967,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40869,7 +40872,7 @@
         <v>2</v>
       </c>
       <c r="AQ192">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR192">
         <v>1.15</v>
@@ -42848,7 +42851,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43054,7 +43057,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43338,7 +43341,7 @@
         <v>1.13</v>
       </c>
       <c r="AP204">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AQ204">
         <v>1.3</v>
@@ -44783,7 +44786,7 @@
         <v>2</v>
       </c>
       <c r="AQ211">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="AR211">
         <v>1.69</v>
@@ -45320,7 +45323,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45732,7 +45735,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -51039,6 +51042,212 @@
       </c>
       <c r="BP241">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="242" spans="1:68">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>7728440</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>69</v>
+      </c>
+      <c r="E242" s="2">
+        <v>45670.6875</v>
+      </c>
+      <c r="F242">
+        <v>22</v>
+      </c>
+      <c r="G242" t="s">
+        <v>80</v>
+      </c>
+      <c r="H242" t="s">
+        <v>73</v>
+      </c>
+      <c r="I242">
+        <v>1</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242">
+        <v>1</v>
+      </c>
+      <c r="L242">
+        <v>1</v>
+      </c>
+      <c r="M242">
+        <v>3</v>
+      </c>
+      <c r="N242">
+        <v>4</v>
+      </c>
+      <c r="O242" t="s">
+        <v>247</v>
+      </c>
+      <c r="P242" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q242">
+        <v>3.5</v>
+      </c>
+      <c r="R242">
+        <v>1.91</v>
+      </c>
+      <c r="S242">
+        <v>4</v>
+      </c>
+      <c r="T242">
+        <v>1.62</v>
+      </c>
+      <c r="U242">
+        <v>2.2</v>
+      </c>
+      <c r="V242">
+        <v>4</v>
+      </c>
+      <c r="W242">
+        <v>1.22</v>
+      </c>
+      <c r="X242">
+        <v>13</v>
+      </c>
+      <c r="Y242">
+        <v>1.04</v>
+      </c>
+      <c r="Z242">
+        <v>2.41</v>
+      </c>
+      <c r="AA242">
+        <v>3.14</v>
+      </c>
+      <c r="AB242">
+        <v>3.13</v>
+      </c>
+      <c r="AC242">
+        <v>1.12</v>
+      </c>
+      <c r="AD242">
+        <v>6.5</v>
+      </c>
+      <c r="AE242">
+        <v>1.51</v>
+      </c>
+      <c r="AF242">
+        <v>2.55</v>
+      </c>
+      <c r="AG242">
+        <v>2.4</v>
+      </c>
+      <c r="AH242">
+        <v>1.48</v>
+      </c>
+      <c r="AI242">
+        <v>2.2</v>
+      </c>
+      <c r="AJ242">
+        <v>1.62</v>
+      </c>
+      <c r="AK242">
+        <v>1.37</v>
+      </c>
+      <c r="AL242">
+        <v>1.39</v>
+      </c>
+      <c r="AM242">
+        <v>1.49</v>
+      </c>
+      <c r="AN242">
+        <v>1.5</v>
+      </c>
+      <c r="AO242">
+        <v>0.5</v>
+      </c>
+      <c r="AP242">
+        <v>1.36</v>
+      </c>
+      <c r="AQ242">
+        <v>0.73</v>
+      </c>
+      <c r="AR242">
+        <v>1.37</v>
+      </c>
+      <c r="AS242">
+        <v>1.23</v>
+      </c>
+      <c r="AT242">
+        <v>2.6</v>
+      </c>
+      <c r="AU242">
+        <v>5</v>
+      </c>
+      <c r="AV242">
+        <v>4</v>
+      </c>
+      <c r="AW242">
+        <v>19</v>
+      </c>
+      <c r="AX242">
+        <v>13</v>
+      </c>
+      <c r="AY242">
+        <v>32</v>
+      </c>
+      <c r="AZ242">
+        <v>20</v>
+      </c>
+      <c r="BA242">
+        <v>11</v>
+      </c>
+      <c r="BB242">
+        <v>5</v>
+      </c>
+      <c r="BC242">
+        <v>16</v>
+      </c>
+      <c r="BD242">
+        <v>1.77</v>
+      </c>
+      <c r="BE242">
+        <v>6.4</v>
+      </c>
+      <c r="BF242">
+        <v>2.28</v>
+      </c>
+      <c r="BG242">
+        <v>1.35</v>
+      </c>
+      <c r="BH242">
+        <v>2.85</v>
+      </c>
+      <c r="BI242">
+        <v>1.6</v>
+      </c>
+      <c r="BJ242">
+        <v>2.14</v>
+      </c>
+      <c r="BK242">
+        <v>1.97</v>
+      </c>
+      <c r="BL242">
+        <v>1.71</v>
+      </c>
+      <c r="BM242">
+        <v>2.5</v>
+      </c>
+      <c r="BN242">
+        <v>1.44</v>
+      </c>
+      <c r="BO242">
+        <v>3.3</v>
+      </c>
+      <c r="BP242">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
@@ -51190,16 +51190,16 @@
         <v>4</v>
       </c>
       <c r="AW242">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AX242">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AY242">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AZ242">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA242">
         <v>11</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="343">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -760,6 +760,12 @@
     <t>['13']</t>
   </si>
   <si>
+    <t>['37']</t>
+  </si>
+  <si>
+    <t>['21', '72', '90+5']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1034,6 +1040,9 @@
   </si>
   <si>
     <t>['58', '62', '90+6']</t>
+  </si>
+  <si>
+    <t>['21', '44', '45+3', '55']</t>
   </si>
 </sst>
 </file>
@@ -1395,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP242"/>
+  <dimension ref="A1:BP247"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1651,7 +1660,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1732,7 +1741,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ2">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2063,7 +2072,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2347,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ5">
         <v>1.36</v>
@@ -2681,7 +2690,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2762,7 +2771,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ7">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2887,7 +2896,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -2965,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ8">
         <v>1.33</v>
@@ -3093,7 +3102,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3789,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ12">
         <v>0.18</v>
@@ -3917,7 +3926,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4123,7 +4132,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4407,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ15">
         <v>0.55</v>
@@ -4616,7 +4625,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ16">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR16">
         <v>1.33</v>
@@ -4819,10 +4828,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5153,7 +5162,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5440,7 +5449,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ20">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5646,7 +5655,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ21">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5771,7 +5780,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5849,7 +5858,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ22">
         <v>1.33</v>
@@ -5977,7 +5986,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6183,7 +6192,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6389,7 +6398,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6595,7 +6604,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6801,7 +6810,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -6882,7 +6891,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ27">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR27">
         <v>1.25</v>
@@ -7213,7 +7222,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7831,7 +7840,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -7909,7 +7918,7 @@
         <v>0</v>
       </c>
       <c r="AP32">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ32">
         <v>0.58</v>
@@ -8037,7 +8046,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8115,7 +8124,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ33">
         <v>1.33</v>
@@ -8449,7 +8458,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -9067,7 +9076,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9145,10 +9154,10 @@
         <v>2</v>
       </c>
       <c r="AP38">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ38">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR38">
         <v>1.41</v>
@@ -9763,7 +9772,7 @@
         <v>2</v>
       </c>
       <c r="AP41">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ41">
         <v>1.33</v>
@@ -9969,7 +9978,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ42">
         <v>1.75</v>
@@ -10178,7 +10187,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ43">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR43">
         <v>0</v>
@@ -10303,7 +10312,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10384,7 +10393,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ44">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR44">
         <v>1.41</v>
@@ -10921,7 +10930,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -10999,7 +11008,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ47">
         <v>0.55</v>
@@ -11205,7 +11214,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ48">
         <v>0.18</v>
@@ -11826,7 +11835,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ51">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR51">
         <v>0.76</v>
@@ -12569,7 +12578,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12650,7 +12659,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ55">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR55">
         <v>1.39</v>
@@ -12775,7 +12784,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -12981,7 +12990,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13187,7 +13196,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13268,7 +13277,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ58">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR58">
         <v>1.22</v>
@@ -13471,10 +13480,10 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ59">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR59">
         <v>1.51</v>
@@ -13599,7 +13608,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14217,7 +14226,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14295,10 +14304,10 @@
         <v>2</v>
       </c>
       <c r="AP63">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ63">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR63">
         <v>1.13</v>
@@ -14835,7 +14844,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15247,7 +15256,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15453,7 +15462,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -15943,7 +15952,7 @@
         <v>1.75</v>
       </c>
       <c r="AP71">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ71">
         <v>1.33</v>
@@ -16071,7 +16080,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16152,7 +16161,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ72">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR72">
         <v>1.35</v>
@@ -16277,7 +16286,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16355,7 +16364,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ73">
         <v>1.75</v>
@@ -16483,7 +16492,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16564,7 +16573,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ74">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR74">
         <v>1.54</v>
@@ -17307,7 +17316,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17513,7 +17522,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17594,7 +17603,7 @@
         <v>2</v>
       </c>
       <c r="AQ79">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR79">
         <v>1.18</v>
@@ -17800,7 +17809,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ80">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR80">
         <v>1.23</v>
@@ -17925,7 +17934,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18006,7 +18015,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ81">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR81">
         <v>1.07</v>
@@ -18131,7 +18140,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18209,7 +18218,7 @@
         <v>0.67</v>
       </c>
       <c r="AP82">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ82">
         <v>1.09</v>
@@ -18337,7 +18346,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19161,7 +19170,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19239,7 +19248,7 @@
         <v>2</v>
       </c>
       <c r="AP87">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ87">
         <v>1.36</v>
@@ -19445,10 +19454,10 @@
         <v>1.25</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ88">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR88">
         <v>1.96</v>
@@ -19573,7 +19582,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19779,7 +19788,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20063,7 +20072,7 @@
         <v>0.33</v>
       </c>
       <c r="AP91">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ91">
         <v>1</v>
@@ -20191,7 +20200,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20475,7 +20484,7 @@
         <v>1.33</v>
       </c>
       <c r="AP93">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ93">
         <v>0.55</v>
@@ -20603,7 +20612,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20684,7 +20693,7 @@
         <v>2</v>
       </c>
       <c r="AQ94">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR94">
         <v>1.16</v>
@@ -20809,7 +20818,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21839,7 +21848,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -21917,7 +21926,7 @@
         <v>2.25</v>
       </c>
       <c r="AP100">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ100">
         <v>1.36</v>
@@ -22332,7 +22341,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ102">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR102">
         <v>1.13</v>
@@ -23281,7 +23290,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23899,7 +23908,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24311,7 +24320,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24517,7 +24526,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24598,7 +24607,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ113">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR113">
         <v>1.63</v>
@@ -24801,10 +24810,10 @@
         <v>1.75</v>
       </c>
       <c r="AP114">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ114">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR114">
         <v>1.43</v>
@@ -24929,7 +24938,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25007,7 +25016,7 @@
         <v>1.67</v>
       </c>
       <c r="AP115">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ115">
         <v>1.33</v>
@@ -25419,10 +25428,10 @@
         <v>0.75</v>
       </c>
       <c r="AP117">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ117">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR117">
         <v>1.16</v>
@@ -25628,7 +25637,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ118">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR118">
         <v>1.69</v>
@@ -25753,7 +25762,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -25831,7 +25840,7 @@
         <v>1</v>
       </c>
       <c r="AP119">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ119">
         <v>1.2</v>
@@ -26037,7 +26046,7 @@
         <v>1.4</v>
       </c>
       <c r="AP120">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ120">
         <v>1.27</v>
@@ -26371,7 +26380,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26658,7 +26667,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ123">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR123">
         <v>1.53</v>
@@ -26783,7 +26792,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27195,7 +27204,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27607,7 +27616,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28019,7 +28028,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28225,7 +28234,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28431,7 +28440,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28843,7 +28852,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -28921,10 +28930,10 @@
         <v>0.8</v>
       </c>
       <c r="AP134">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR134">
         <v>1.4</v>
@@ -29049,7 +29058,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29127,7 +29136,7 @@
         <v>0.83</v>
       </c>
       <c r="AP135">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ135">
         <v>1.2</v>
@@ -29333,10 +29342,10 @@
         <v>1.4</v>
       </c>
       <c r="AP136">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ136">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR136">
         <v>1.55</v>
@@ -29542,7 +29551,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ137">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR137">
         <v>1.67</v>
@@ -29667,7 +29676,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -29748,7 +29757,7 @@
         <v>1.45</v>
       </c>
       <c r="AQ138">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR138">
         <v>1.52</v>
@@ -30285,7 +30294,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30491,7 +30500,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30572,7 +30581,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ142">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR142">
         <v>1.16</v>
@@ -30697,7 +30706,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30903,7 +30912,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31315,7 +31324,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31727,7 +31736,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32014,7 +32023,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ149">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR149">
         <v>1.82</v>
@@ -32423,7 +32432,7 @@
         <v>1</v>
       </c>
       <c r="AP151">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ151">
         <v>1</v>
@@ -32629,10 +32638,10 @@
         <v>1.14</v>
       </c>
       <c r="AP152">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ152">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR152">
         <v>1.54</v>
@@ -32757,7 +32766,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33041,10 +33050,10 @@
         <v>1.17</v>
       </c>
       <c r="AP154">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ154">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR154">
         <v>1.67</v>
@@ -33375,7 +33384,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33453,10 +33462,10 @@
         <v>1.83</v>
       </c>
       <c r="AP156">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ156">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR156">
         <v>1.44</v>
@@ -34277,7 +34286,7 @@
         <v>1.17</v>
       </c>
       <c r="AP160">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ160">
         <v>1.27</v>
@@ -34689,7 +34698,7 @@
         <v>1</v>
       </c>
       <c r="AP162">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ162">
         <v>1.27</v>
@@ -35023,7 +35032,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35101,7 +35110,7 @@
         <v>1.38</v>
       </c>
       <c r="AP164">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ164">
         <v>1.75</v>
@@ -35310,7 +35319,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ165">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR165">
         <v>1.7</v>
@@ -35641,7 +35650,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36053,7 +36062,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36671,7 +36680,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -36958,7 +36967,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ173">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR173">
         <v>1.44</v>
@@ -37289,7 +37298,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37367,7 +37376,7 @@
         <v>1</v>
       </c>
       <c r="AP175">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ175">
         <v>1</v>
@@ -37701,7 +37710,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -37988,7 +37997,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ178">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR178">
         <v>1.71</v>
@@ -38113,7 +38122,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38194,7 +38203,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ179">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR179">
         <v>1.71</v>
@@ -38319,7 +38328,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38812,7 +38821,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ182">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR182">
         <v>1.26</v>
@@ -39143,7 +39152,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39221,7 +39230,7 @@
         <v>0.88</v>
       </c>
       <c r="AP184">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ184">
         <v>0.82</v>
@@ -39427,7 +39436,7 @@
         <v>0.86</v>
       </c>
       <c r="AP185">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ185">
         <v>1</v>
@@ -39633,7 +39642,7 @@
         <v>0.13</v>
       </c>
       <c r="AP186">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ186">
         <v>0.45</v>
@@ -39839,7 +39848,7 @@
         <v>0.75</v>
       </c>
       <c r="AP187">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ187">
         <v>0.58</v>
@@ -39967,7 +39976,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40254,7 +40263,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ189">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR189">
         <v>1.53</v>
@@ -40585,7 +40594,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40791,7 +40800,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -40997,7 +41006,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41078,7 +41087,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ193">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR193">
         <v>1.13</v>
@@ -41203,7 +41212,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42105,7 +42114,7 @@
         <v>1.25</v>
       </c>
       <c r="AP198">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ198">
         <v>1.09</v>
@@ -42439,7 +42448,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42517,7 +42526,7 @@
         <v>0.11</v>
       </c>
       <c r="AP200">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ200">
         <v>0.45</v>
@@ -42726,7 +42735,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ201">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR201">
         <v>1.46</v>
@@ -42851,7 +42860,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43057,7 +43066,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43135,7 +43144,7 @@
         <v>1.6</v>
       </c>
       <c r="AP203">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ203">
         <v>1.33</v>
@@ -43341,10 +43350,10 @@
         <v>1.13</v>
       </c>
       <c r="AP204">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ204">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR204">
         <v>1.41</v>
@@ -43550,7 +43559,7 @@
         <v>2</v>
       </c>
       <c r="AQ205">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR205">
         <v>1.69</v>
@@ -43675,7 +43684,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -43753,7 +43762,7 @@
         <v>0.88</v>
       </c>
       <c r="AP206">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ206">
         <v>1</v>
@@ -44087,7 +44096,7 @@
         <v>94</v>
       </c>
       <c r="P208" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44705,7 +44714,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -44911,7 +44920,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -44992,7 +45001,7 @@
         <v>1.3</v>
       </c>
       <c r="AQ212">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AR212">
         <v>1.69</v>
@@ -45117,7 +45126,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45323,7 +45332,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45735,7 +45744,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46637,10 +46646,10 @@
         <v>1.1</v>
       </c>
       <c r="AP220">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AQ220">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AR220">
         <v>1.23</v>
@@ -46843,10 +46852,10 @@
         <v>1.56</v>
       </c>
       <c r="AP221">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ221">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR221">
         <v>1.48</v>
@@ -46971,7 +46980,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47383,7 +47392,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47461,7 +47470,7 @@
         <v>0.8</v>
       </c>
       <c r="AP224">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AQ224">
         <v>1</v>
@@ -47795,7 +47804,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -47876,7 +47885,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ226">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AR226">
         <v>1.73</v>
@@ -48001,7 +48010,7 @@
         <v>200</v>
       </c>
       <c r="P227" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q227">
         <v>2.25</v>
@@ -48082,7 +48091,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ227">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR227">
         <v>1.67</v>
@@ -48413,7 +48422,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48619,7 +48628,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48697,7 +48706,7 @@
         <v>1.3</v>
       </c>
       <c r="AP230">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ230">
         <v>1.27</v>
@@ -48825,7 +48834,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49649,7 +49658,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50473,7 +50482,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51091,7 +51100,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51169,7 +51178,7 @@
         <v>0.5</v>
       </c>
       <c r="AP242">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AQ242">
         <v>0.73</v>
@@ -51248,6 +51257,1036 @@
       </c>
       <c r="BP242">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="243" spans="1:68">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>7728443</v>
+      </c>
+      <c r="C243" t="s">
+        <v>68</v>
+      </c>
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="2">
+        <v>45674.6875</v>
+      </c>
+      <c r="F243">
+        <v>23</v>
+      </c>
+      <c r="G243" t="s">
+        <v>87</v>
+      </c>
+      <c r="H243" t="s">
+        <v>89</v>
+      </c>
+      <c r="I243">
+        <v>0</v>
+      </c>
+      <c r="J243">
+        <v>1</v>
+      </c>
+      <c r="K243">
+        <v>1</v>
+      </c>
+      <c r="L243">
+        <v>0</v>
+      </c>
+      <c r="M243">
+        <v>1</v>
+      </c>
+      <c r="N243">
+        <v>1</v>
+      </c>
+      <c r="O243" t="s">
+        <v>94</v>
+      </c>
+      <c r="P243" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q243">
+        <v>4.6</v>
+      </c>
+      <c r="R243">
+        <v>1.93</v>
+      </c>
+      <c r="S243">
+        <v>2.55</v>
+      </c>
+      <c r="T243">
+        <v>1.52</v>
+      </c>
+      <c r="U243">
+        <v>2.35</v>
+      </c>
+      <c r="V243">
+        <v>3.4</v>
+      </c>
+      <c r="W243">
+        <v>1.27</v>
+      </c>
+      <c r="X243">
+        <v>9.75</v>
+      </c>
+      <c r="Y243">
+        <v>1.04</v>
+      </c>
+      <c r="Z243">
+        <v>4.4</v>
+      </c>
+      <c r="AA243">
+        <v>3.3</v>
+      </c>
+      <c r="AB243">
+        <v>1.92</v>
+      </c>
+      <c r="AC243">
+        <v>1.1</v>
+      </c>
+      <c r="AD243">
+        <v>6.5</v>
+      </c>
+      <c r="AE243">
+        <v>1.5</v>
+      </c>
+      <c r="AF243">
+        <v>2.4</v>
+      </c>
+      <c r="AG243">
+        <v>2.41</v>
+      </c>
+      <c r="AH243">
+        <v>1.5</v>
+      </c>
+      <c r="AI243">
+        <v>2.2</v>
+      </c>
+      <c r="AJ243">
+        <v>1.6</v>
+      </c>
+      <c r="AK243">
+        <v>1.83</v>
+      </c>
+      <c r="AL243">
+        <v>1.28</v>
+      </c>
+      <c r="AM243">
+        <v>1.2</v>
+      </c>
+      <c r="AN243">
+        <v>0.8</v>
+      </c>
+      <c r="AO243">
+        <v>1.27</v>
+      </c>
+      <c r="AP243">
+        <v>0.73</v>
+      </c>
+      <c r="AQ243">
+        <v>1.42</v>
+      </c>
+      <c r="AR243">
+        <v>1.18</v>
+      </c>
+      <c r="AS243">
+        <v>1.26</v>
+      </c>
+      <c r="AT243">
+        <v>2.44</v>
+      </c>
+      <c r="AU243">
+        <v>5</v>
+      </c>
+      <c r="AV243">
+        <v>10</v>
+      </c>
+      <c r="AW243">
+        <v>5</v>
+      </c>
+      <c r="AX243">
+        <v>8</v>
+      </c>
+      <c r="AY243">
+        <v>10</v>
+      </c>
+      <c r="AZ243">
+        <v>20</v>
+      </c>
+      <c r="BA243">
+        <v>2</v>
+      </c>
+      <c r="BB243">
+        <v>4</v>
+      </c>
+      <c r="BC243">
+        <v>6</v>
+      </c>
+      <c r="BD243">
+        <v>2.4</v>
+      </c>
+      <c r="BE243">
+        <v>6.4</v>
+      </c>
+      <c r="BF243">
+        <v>1.7</v>
+      </c>
+      <c r="BG243">
+        <v>1.4</v>
+      </c>
+      <c r="BH243">
+        <v>2.65</v>
+      </c>
+      <c r="BI243">
+        <v>1.68</v>
+      </c>
+      <c r="BJ243">
+        <v>2.02</v>
+      </c>
+      <c r="BK243">
+        <v>2.08</v>
+      </c>
+      <c r="BL243">
+        <v>1.63</v>
+      </c>
+      <c r="BM243">
+        <v>2.65</v>
+      </c>
+      <c r="BN243">
+        <v>1.4</v>
+      </c>
+      <c r="BO243">
+        <v>3.55</v>
+      </c>
+      <c r="BP243">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="244" spans="1:68">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>7728446</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="2">
+        <v>45675.51041666666</v>
+      </c>
+      <c r="F244">
+        <v>23</v>
+      </c>
+      <c r="G244" t="s">
+        <v>80</v>
+      </c>
+      <c r="H244" t="s">
+        <v>72</v>
+      </c>
+      <c r="I244">
+        <v>0</v>
+      </c>
+      <c r="J244">
+        <v>3</v>
+      </c>
+      <c r="K244">
+        <v>3</v>
+      </c>
+      <c r="L244">
+        <v>1</v>
+      </c>
+      <c r="M244">
+        <v>4</v>
+      </c>
+      <c r="N244">
+        <v>5</v>
+      </c>
+      <c r="O244" t="s">
+        <v>224</v>
+      </c>
+      <c r="P244" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q244">
+        <v>3.4</v>
+      </c>
+      <c r="R244">
+        <v>1.91</v>
+      </c>
+      <c r="S244">
+        <v>3.75</v>
+      </c>
+      <c r="T244">
+        <v>1.62</v>
+      </c>
+      <c r="U244">
+        <v>2.2</v>
+      </c>
+      <c r="V244">
+        <v>4</v>
+      </c>
+      <c r="W244">
+        <v>1.22</v>
+      </c>
+      <c r="X244">
+        <v>13</v>
+      </c>
+      <c r="Y244">
+        <v>1.04</v>
+      </c>
+      <c r="Z244">
+        <v>2.43</v>
+      </c>
+      <c r="AA244">
+        <v>2.83</v>
+      </c>
+      <c r="AB244">
+        <v>2.81</v>
+      </c>
+      <c r="AC244">
+        <v>1.11</v>
+      </c>
+      <c r="AD244">
+        <v>6.25</v>
+      </c>
+      <c r="AE244">
+        <v>1.53</v>
+      </c>
+      <c r="AF244">
+        <v>2.3</v>
+      </c>
+      <c r="AG244">
+        <v>2.62</v>
+      </c>
+      <c r="AH244">
+        <v>1.43</v>
+      </c>
+      <c r="AI244">
+        <v>2.2</v>
+      </c>
+      <c r="AJ244">
+        <v>1.62</v>
+      </c>
+      <c r="AK244">
+        <v>1.35</v>
+      </c>
+      <c r="AL244">
+        <v>1.38</v>
+      </c>
+      <c r="AM244">
+        <v>1.51</v>
+      </c>
+      <c r="AN244">
+        <v>1.36</v>
+      </c>
+      <c r="AO244">
+        <v>1</v>
+      </c>
+      <c r="AP244">
+        <v>1.25</v>
+      </c>
+      <c r="AQ244">
+        <v>1.18</v>
+      </c>
+      <c r="AR244">
+        <v>1.4</v>
+      </c>
+      <c r="AS244">
+        <v>1.18</v>
+      </c>
+      <c r="AT244">
+        <v>2.58</v>
+      </c>
+      <c r="AU244">
+        <v>6</v>
+      </c>
+      <c r="AV244">
+        <v>9</v>
+      </c>
+      <c r="AW244">
+        <v>12</v>
+      </c>
+      <c r="AX244">
+        <v>5</v>
+      </c>
+      <c r="AY244">
+        <v>19</v>
+      </c>
+      <c r="AZ244">
+        <v>16</v>
+      </c>
+      <c r="BA244">
+        <v>10</v>
+      </c>
+      <c r="BB244">
+        <v>2</v>
+      </c>
+      <c r="BC244">
+        <v>12</v>
+      </c>
+      <c r="BD244">
+        <v>1.74</v>
+      </c>
+      <c r="BE244">
+        <v>6.5</v>
+      </c>
+      <c r="BF244">
+        <v>2.33</v>
+      </c>
+      <c r="BG244">
+        <v>1.36</v>
+      </c>
+      <c r="BH244">
+        <v>2.8</v>
+      </c>
+      <c r="BI244">
+        <v>1.63</v>
+      </c>
+      <c r="BJ244">
+        <v>2.08</v>
+      </c>
+      <c r="BK244">
+        <v>2.02</v>
+      </c>
+      <c r="BL244">
+        <v>1.67</v>
+      </c>
+      <c r="BM244">
+        <v>2.63</v>
+      </c>
+      <c r="BN244">
+        <v>1.41</v>
+      </c>
+      <c r="BO244">
+        <v>3.4</v>
+      </c>
+      <c r="BP244">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="245" spans="1:68">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>7728445</v>
+      </c>
+      <c r="C245" t="s">
+        <v>68</v>
+      </c>
+      <c r="D245" t="s">
+        <v>69</v>
+      </c>
+      <c r="E245" s="2">
+        <v>45675.60416666666</v>
+      </c>
+      <c r="F245">
+        <v>23</v>
+      </c>
+      <c r="G245" t="s">
+        <v>73</v>
+      </c>
+      <c r="H245" t="s">
+        <v>85</v>
+      </c>
+      <c r="I245">
+        <v>1</v>
+      </c>
+      <c r="J245">
+        <v>0</v>
+      </c>
+      <c r="K245">
+        <v>1</v>
+      </c>
+      <c r="L245">
+        <v>1</v>
+      </c>
+      <c r="M245">
+        <v>1</v>
+      </c>
+      <c r="N245">
+        <v>2</v>
+      </c>
+      <c r="O245" t="s">
+        <v>188</v>
+      </c>
+      <c r="P245" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q245">
+        <v>2.63</v>
+      </c>
+      <c r="R245">
+        <v>2.05</v>
+      </c>
+      <c r="S245">
+        <v>4.75</v>
+      </c>
+      <c r="T245">
+        <v>1.5</v>
+      </c>
+      <c r="U245">
+        <v>2.5</v>
+      </c>
+      <c r="V245">
+        <v>3.4</v>
+      </c>
+      <c r="W245">
+        <v>1.3</v>
+      </c>
+      <c r="X245">
+        <v>10</v>
+      </c>
+      <c r="Y245">
+        <v>1.06</v>
+      </c>
+      <c r="Z245">
+        <v>1.97</v>
+      </c>
+      <c r="AA245">
+        <v>3.15</v>
+      </c>
+      <c r="AB245">
+        <v>3.9</v>
+      </c>
+      <c r="AC245">
+        <v>1.08</v>
+      </c>
+      <c r="AD245">
+        <v>7.5</v>
+      </c>
+      <c r="AE245">
+        <v>1.42</v>
+      </c>
+      <c r="AF245">
+        <v>2.8</v>
+      </c>
+      <c r="AG245">
+        <v>2.15</v>
+      </c>
+      <c r="AH245">
+        <v>1.62</v>
+      </c>
+      <c r="AI245">
+        <v>2</v>
+      </c>
+      <c r="AJ245">
+        <v>1.73</v>
+      </c>
+      <c r="AK245">
+        <v>1.24</v>
+      </c>
+      <c r="AL245">
+        <v>1.31</v>
+      </c>
+      <c r="AM245">
+        <v>1.8</v>
+      </c>
+      <c r="AN245">
+        <v>2.09</v>
+      </c>
+      <c r="AO245">
+        <v>1.09</v>
+      </c>
+      <c r="AP245">
+        <v>2</v>
+      </c>
+      <c r="AQ245">
+        <v>1.08</v>
+      </c>
+      <c r="AR245">
+        <v>1.49</v>
+      </c>
+      <c r="AS245">
+        <v>1.29</v>
+      </c>
+      <c r="AT245">
+        <v>2.78</v>
+      </c>
+      <c r="AU245">
+        <v>5</v>
+      </c>
+      <c r="AV245">
+        <v>5</v>
+      </c>
+      <c r="AW245">
+        <v>6</v>
+      </c>
+      <c r="AX245">
+        <v>6</v>
+      </c>
+      <c r="AY245">
+        <v>12</v>
+      </c>
+      <c r="AZ245">
+        <v>11</v>
+      </c>
+      <c r="BA245">
+        <v>3</v>
+      </c>
+      <c r="BB245">
+        <v>1</v>
+      </c>
+      <c r="BC245">
+        <v>4</v>
+      </c>
+      <c r="BD245">
+        <v>1.58</v>
+      </c>
+      <c r="BE245">
+        <v>6.5</v>
+      </c>
+      <c r="BF245">
+        <v>2.65</v>
+      </c>
+      <c r="BG245">
+        <v>1.38</v>
+      </c>
+      <c r="BH245">
+        <v>2.7</v>
+      </c>
+      <c r="BI245">
+        <v>1.66</v>
+      </c>
+      <c r="BJ245">
+        <v>2.04</v>
+      </c>
+      <c r="BK245">
+        <v>2.06</v>
+      </c>
+      <c r="BL245">
+        <v>1.64</v>
+      </c>
+      <c r="BM245">
+        <v>2.65</v>
+      </c>
+      <c r="BN245">
+        <v>1.4</v>
+      </c>
+      <c r="BO245">
+        <v>3.45</v>
+      </c>
+      <c r="BP245">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="246" spans="1:68">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7728447</v>
+      </c>
+      <c r="C246" t="s">
+        <v>68</v>
+      </c>
+      <c r="D246" t="s">
+        <v>69</v>
+      </c>
+      <c r="E246" s="2">
+        <v>45675.60416666666</v>
+      </c>
+      <c r="F246">
+        <v>23</v>
+      </c>
+      <c r="G246" t="s">
+        <v>76</v>
+      </c>
+      <c r="H246" t="s">
+        <v>79</v>
+      </c>
+      <c r="I246">
+        <v>1</v>
+      </c>
+      <c r="J246">
+        <v>0</v>
+      </c>
+      <c r="K246">
+        <v>1</v>
+      </c>
+      <c r="L246">
+        <v>1</v>
+      </c>
+      <c r="M246">
+        <v>1</v>
+      </c>
+      <c r="N246">
+        <v>2</v>
+      </c>
+      <c r="O246" t="s">
+        <v>248</v>
+      </c>
+      <c r="P246" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q246">
+        <v>2.9</v>
+      </c>
+      <c r="R246">
+        <v>1.9</v>
+      </c>
+      <c r="S246">
+        <v>3.9</v>
+      </c>
+      <c r="T246">
+        <v>1.52</v>
+      </c>
+      <c r="U246">
+        <v>2.35</v>
+      </c>
+      <c r="V246">
+        <v>3.5</v>
+      </c>
+      <c r="W246">
+        <v>1.26</v>
+      </c>
+      <c r="X246">
+        <v>10</v>
+      </c>
+      <c r="Y246">
+        <v>1.04</v>
+      </c>
+      <c r="Z246">
+        <v>2.35</v>
+      </c>
+      <c r="AA246">
+        <v>2.9</v>
+      </c>
+      <c r="AB246">
+        <v>3.2</v>
+      </c>
+      <c r="AC246">
+        <v>1.1</v>
+      </c>
+      <c r="AD246">
+        <v>6.5</v>
+      </c>
+      <c r="AE246">
+        <v>1.49</v>
+      </c>
+      <c r="AF246">
+        <v>2.4</v>
+      </c>
+      <c r="AG246">
+        <v>2.55</v>
+      </c>
+      <c r="AH246">
+        <v>1.46</v>
+      </c>
+      <c r="AI246">
+        <v>2.1</v>
+      </c>
+      <c r="AJ246">
+        <v>1.63</v>
+      </c>
+      <c r="AK246">
+        <v>1.32</v>
+      </c>
+      <c r="AL246">
+        <v>1.34</v>
+      </c>
+      <c r="AM246">
+        <v>1.61</v>
+      </c>
+      <c r="AN246">
+        <v>1.73</v>
+      </c>
+      <c r="AO246">
+        <v>1.3</v>
+      </c>
+      <c r="AP246">
+        <v>1.67</v>
+      </c>
+      <c r="AQ246">
+        <v>1.27</v>
+      </c>
+      <c r="AR246">
+        <v>1.56</v>
+      </c>
+      <c r="AS246">
+        <v>1.23</v>
+      </c>
+      <c r="AT246">
+        <v>2.79</v>
+      </c>
+      <c r="AU246">
+        <v>4</v>
+      </c>
+      <c r="AV246">
+        <v>5</v>
+      </c>
+      <c r="AW246">
+        <v>8</v>
+      </c>
+      <c r="AX246">
+        <v>2</v>
+      </c>
+      <c r="AY246">
+        <v>13</v>
+      </c>
+      <c r="AZ246">
+        <v>8</v>
+      </c>
+      <c r="BA246">
+        <v>4</v>
+      </c>
+      <c r="BB246">
+        <v>5</v>
+      </c>
+      <c r="BC246">
+        <v>9</v>
+      </c>
+      <c r="BD246">
+        <v>1.74</v>
+      </c>
+      <c r="BE246">
+        <v>6.25</v>
+      </c>
+      <c r="BF246">
+        <v>2.33</v>
+      </c>
+      <c r="BG246">
+        <v>1.44</v>
+      </c>
+      <c r="BH246">
+        <v>2.5</v>
+      </c>
+      <c r="BI246">
+        <v>1.75</v>
+      </c>
+      <c r="BJ246">
+        <v>1.92</v>
+      </c>
+      <c r="BK246">
+        <v>2.23</v>
+      </c>
+      <c r="BL246">
+        <v>1.56</v>
+      </c>
+      <c r="BM246">
+        <v>2.9</v>
+      </c>
+      <c r="BN246">
+        <v>1.34</v>
+      </c>
+      <c r="BO246">
+        <v>3.8</v>
+      </c>
+      <c r="BP246">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="247" spans="1:68">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>7728449</v>
+      </c>
+      <c r="C247" t="s">
+        <v>68</v>
+      </c>
+      <c r="D247" t="s">
+        <v>69</v>
+      </c>
+      <c r="E247" s="2">
+        <v>45675.70833333334</v>
+      </c>
+      <c r="F247">
+        <v>23</v>
+      </c>
+      <c r="G247" t="s">
+        <v>82</v>
+      </c>
+      <c r="H247" t="s">
+        <v>70</v>
+      </c>
+      <c r="I247">
+        <v>1</v>
+      </c>
+      <c r="J247">
+        <v>0</v>
+      </c>
+      <c r="K247">
+        <v>1</v>
+      </c>
+      <c r="L247">
+        <v>3</v>
+      </c>
+      <c r="M247">
+        <v>1</v>
+      </c>
+      <c r="N247">
+        <v>4</v>
+      </c>
+      <c r="O247" t="s">
+        <v>249</v>
+      </c>
+      <c r="P247" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q247">
+        <v>2.45</v>
+      </c>
+      <c r="R247">
+        <v>2.05</v>
+      </c>
+      <c r="S247">
+        <v>4.33</v>
+      </c>
+      <c r="T247">
+        <v>1.41</v>
+      </c>
+      <c r="U247">
+        <v>2.65</v>
+      </c>
+      <c r="V247">
+        <v>2.85</v>
+      </c>
+      <c r="W247">
+        <v>1.36</v>
+      </c>
+      <c r="X247">
+        <v>7.5</v>
+      </c>
+      <c r="Y247">
+        <v>1.07</v>
+      </c>
+      <c r="Z247">
+        <v>1.95</v>
+      </c>
+      <c r="AA247">
+        <v>3.15</v>
+      </c>
+      <c r="AB247">
+        <v>4.1</v>
+      </c>
+      <c r="AC247">
+        <v>1.07</v>
+      </c>
+      <c r="AD247">
+        <v>8</v>
+      </c>
+      <c r="AE247">
+        <v>1.36</v>
+      </c>
+      <c r="AF247">
+        <v>3.1</v>
+      </c>
+      <c r="AG247">
+        <v>2</v>
+      </c>
+      <c r="AH247">
+        <v>1.71</v>
+      </c>
+      <c r="AI247">
+        <v>1.87</v>
+      </c>
+      <c r="AJ247">
+        <v>1.82</v>
+      </c>
+      <c r="AK247">
+        <v>1.23</v>
+      </c>
+      <c r="AL247">
+        <v>1.29</v>
+      </c>
+      <c r="AM247">
+        <v>1.85</v>
+      </c>
+      <c r="AN247">
+        <v>2</v>
+      </c>
+      <c r="AO247">
+        <v>1.5</v>
+      </c>
+      <c r="AP247">
+        <v>2.09</v>
+      </c>
+      <c r="AQ247">
+        <v>1.36</v>
+      </c>
+      <c r="AR247">
+        <v>1.54</v>
+      </c>
+      <c r="AS247">
+        <v>1.11</v>
+      </c>
+      <c r="AT247">
+        <v>2.65</v>
+      </c>
+      <c r="AU247">
+        <v>7</v>
+      </c>
+      <c r="AV247">
+        <v>3</v>
+      </c>
+      <c r="AW247">
+        <v>11</v>
+      </c>
+      <c r="AX247">
+        <v>9</v>
+      </c>
+      <c r="AY247">
+        <v>19</v>
+      </c>
+      <c r="AZ247">
+        <v>16</v>
+      </c>
+      <c r="BA247">
+        <v>2</v>
+      </c>
+      <c r="BB247">
+        <v>6</v>
+      </c>
+      <c r="BC247">
+        <v>8</v>
+      </c>
+      <c r="BD247">
+        <v>1.49</v>
+      </c>
+      <c r="BE247">
+        <v>6.75</v>
+      </c>
+      <c r="BF247">
+        <v>2.9</v>
+      </c>
+      <c r="BG247">
+        <v>1.36</v>
+      </c>
+      <c r="BH247">
+        <v>2.8</v>
+      </c>
+      <c r="BI247">
+        <v>1.6</v>
+      </c>
+      <c r="BJ247">
+        <v>2.14</v>
+      </c>
+      <c r="BK247">
+        <v>1.97</v>
+      </c>
+      <c r="BL247">
+        <v>1.71</v>
+      </c>
+      <c r="BM247">
+        <v>2.5</v>
+      </c>
+      <c r="BN247">
+        <v>1.44</v>
+      </c>
+      <c r="BO247">
+        <v>3.3</v>
+      </c>
+      <c r="BP247">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="347">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -766,6 +766,12 @@
     <t>['21', '72', '90+5']</t>
   </si>
   <si>
+    <t>['18', '36', '42', '46', '64', '73']</t>
+  </si>
+  <si>
+    <t>['77', '78']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1043,6 +1049,12 @@
   </si>
   <si>
     <t>['21', '44', '45+3', '55']</t>
+  </si>
+  <si>
+    <t>['39', '69']</t>
+  </si>
+  <si>
+    <t>['50', '90+6']</t>
   </si>
 </sst>
 </file>
@@ -1404,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP247"/>
+  <dimension ref="A1:BP252"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1660,7 +1672,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1947,7 +1959,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ3">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2072,7 +2084,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2690,7 +2702,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2896,7 +2908,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3102,7 +3114,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3180,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ9">
         <v>1.75</v>
@@ -3386,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10">
         <v>0.58</v>
@@ -3595,7 +3607,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ11">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3801,7 +3813,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ12">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3926,7 +3938,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4004,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ13">
         <v>0.73</v>
@@ -4132,7 +4144,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -4213,7 +4225,7 @@
         <v>2</v>
       </c>
       <c r="AQ14">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -5162,7 +5174,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5652,7 +5664,7 @@
         <v>3</v>
       </c>
       <c r="AP21">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ21">
         <v>1.42</v>
@@ -5780,7 +5792,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5986,7 +5998,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6192,7 +6204,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6273,7 +6285,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ24">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR24">
         <v>2.51</v>
@@ -6398,7 +6410,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6604,7 +6616,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6685,7 +6697,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ26">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR26">
         <v>1.33</v>
@@ -6810,7 +6822,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7094,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ28">
         <v>1.09</v>
@@ -7222,7 +7234,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7300,7 +7312,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
         <v>1.36</v>
@@ -7509,7 +7521,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ30">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR30">
         <v>1.73</v>
@@ -7840,7 +7852,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8046,7 +8058,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8333,7 +8345,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ34">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR34">
         <v>1.17</v>
@@ -8458,7 +8470,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8745,7 +8757,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ36">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR36">
         <v>2.09</v>
@@ -9076,7 +9088,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -10184,7 +10196,7 @@
         <v>0</v>
       </c>
       <c r="AP43">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ43">
         <v>1.27</v>
@@ -10312,7 +10324,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10390,7 +10402,7 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ44">
         <v>1.18</v>
@@ -10805,7 +10817,7 @@
         <v>2</v>
       </c>
       <c r="AQ46">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR46">
         <v>1.47</v>
@@ -10930,7 +10942,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11217,7 +11229,7 @@
         <v>2</v>
       </c>
       <c r="AQ48">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR48">
         <v>1.67</v>
@@ -11423,7 +11435,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ49">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR49">
         <v>1.38</v>
@@ -11626,7 +11638,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ50">
         <v>1.09</v>
@@ -12244,7 +12256,7 @@
         <v>2.33</v>
       </c>
       <c r="AP53">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ53">
         <v>1.33</v>
@@ -12453,7 +12465,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ54">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR54">
         <v>1.24</v>
@@ -12578,7 +12590,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12784,7 +12796,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -12862,7 +12874,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ56">
         <v>1.36</v>
@@ -12990,7 +13002,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13196,7 +13208,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13608,7 +13620,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -13892,7 +13904,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ61">
         <v>1.33</v>
@@ -14226,7 +14238,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14510,7 +14522,7 @@
         <v>3</v>
       </c>
       <c r="AP64">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ64">
         <v>2.09</v>
@@ -14844,7 +14856,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -14922,7 +14934,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ66">
         <v>0.73</v>
@@ -15131,7 +15143,7 @@
         <v>2</v>
       </c>
       <c r="AQ67">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR67">
         <v>1.16</v>
@@ -15256,7 +15268,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15337,7 +15349,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ68">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR68">
         <v>1.07</v>
@@ -15462,7 +15474,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -15749,7 +15761,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ70">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR70">
         <v>1.04</v>
@@ -16080,7 +16092,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16286,7 +16298,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16492,7 +16504,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -16570,7 +16582,7 @@
         <v>2</v>
       </c>
       <c r="AP74">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ74">
         <v>1.36</v>
@@ -16776,10 +16788,10 @@
         <v>0.33</v>
       </c>
       <c r="AP75">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ75">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR75">
         <v>1.58</v>
@@ -16985,7 +16997,7 @@
         <v>2</v>
       </c>
       <c r="AQ76">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR76">
         <v>1.57</v>
@@ -17316,7 +17328,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17394,7 +17406,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ78">
         <v>0.58</v>
@@ -17522,7 +17534,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17934,7 +17946,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18140,7 +18152,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18346,7 +18358,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -18424,7 +18436,7 @@
         <v>3</v>
       </c>
       <c r="AP83">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ83">
         <v>2.09</v>
@@ -18630,7 +18642,7 @@
         <v>2.33</v>
       </c>
       <c r="AP84">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ84">
         <v>0.82</v>
@@ -19170,7 +19182,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19582,7 +19594,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19663,7 +19675,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ89">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR89">
         <v>1.46</v>
@@ -19788,7 +19800,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20075,7 +20087,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ91">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR91">
         <v>1.18</v>
@@ -20200,7 +20212,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20612,7 +20624,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20818,7 +20830,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21102,7 +21114,7 @@
         <v>1.75</v>
       </c>
       <c r="AP96">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ96">
         <v>1.33</v>
@@ -21311,7 +21323,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ97">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR97">
         <v>1.7</v>
@@ -21514,7 +21526,7 @@
         <v>0.67</v>
       </c>
       <c r="AP98">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ98">
         <v>1.27</v>
@@ -21723,7 +21735,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ99">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR99">
         <v>1.46</v>
@@ -21848,7 +21860,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -22753,7 +22765,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ104">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR104">
         <v>1.71</v>
@@ -22956,7 +22968,7 @@
         <v>1.4</v>
       </c>
       <c r="AP105">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ105">
         <v>1.33</v>
@@ -23290,7 +23302,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23577,7 +23589,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ108">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR108">
         <v>1.17</v>
@@ -23908,7 +23920,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -23986,7 +23998,7 @@
         <v>0.8</v>
       </c>
       <c r="AP110">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ110">
         <v>1.75</v>
@@ -24320,7 +24332,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24526,7 +24538,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24604,7 +24616,7 @@
         <v>2</v>
       </c>
       <c r="AP113">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ113">
         <v>1.36</v>
@@ -24938,7 +24950,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25222,10 +25234,10 @@
         <v>0.2</v>
       </c>
       <c r="AP116">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ116">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR116">
         <v>1.47</v>
@@ -25634,7 +25646,7 @@
         <v>1.4</v>
       </c>
       <c r="AP118">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ118">
         <v>1.08</v>
@@ -25762,7 +25774,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -25843,7 +25855,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ119">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR119">
         <v>1.68</v>
@@ -26049,7 +26061,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ120">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR120">
         <v>1.6</v>
@@ -26380,7 +26392,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26458,10 +26470,10 @@
         <v>1</v>
       </c>
       <c r="AP122">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ122">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR122">
         <v>1.4</v>
@@ -26792,7 +26804,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27204,7 +27216,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27282,7 +27294,7 @@
         <v>1.8</v>
       </c>
       <c r="AP126">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ126">
         <v>1.36</v>
@@ -27616,7 +27628,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28028,7 +28040,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28234,7 +28246,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28440,7 +28452,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28727,7 +28739,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ133">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR133">
         <v>1.15</v>
@@ -28852,7 +28864,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29058,7 +29070,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29139,7 +29151,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ135">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR135">
         <v>1.12</v>
@@ -29548,7 +29560,7 @@
         <v>2.2</v>
       </c>
       <c r="AP137">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ137">
         <v>1.36</v>
@@ -29676,7 +29688,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -29754,7 +29766,7 @@
         <v>1.17</v>
       </c>
       <c r="AP138">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ138">
         <v>1.08</v>
@@ -30294,7 +30306,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30500,7 +30512,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30706,7 +30718,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30912,7 +30924,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31324,7 +31336,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31608,7 +31620,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ147">
         <v>1.09</v>
@@ -31736,7 +31748,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32435,7 +32447,7 @@
         <v>2</v>
       </c>
       <c r="AQ151">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR151">
         <v>1.43</v>
@@ -32766,7 +32778,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -32844,7 +32856,7 @@
         <v>0.83</v>
       </c>
       <c r="AP153">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ153">
         <v>1.27</v>
@@ -33256,7 +33268,7 @@
         <v>1</v>
       </c>
       <c r="AP155">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ155">
         <v>0.82</v>
@@ -33384,7 +33396,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -33671,7 +33683,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ157">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR157">
         <v>1.49</v>
@@ -33877,7 +33889,7 @@
         <v>2</v>
       </c>
       <c r="AQ158">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR158">
         <v>1.68</v>
@@ -34080,10 +34092,10 @@
         <v>1.14</v>
       </c>
       <c r="AP159">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ159">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR159">
         <v>1.75</v>
@@ -34289,7 +34301,7 @@
         <v>0.73</v>
       </c>
       <c r="AQ160">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR160">
         <v>1.21</v>
@@ -34492,7 +34504,7 @@
         <v>1</v>
       </c>
       <c r="AP161">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ161">
         <v>1</v>
@@ -34701,7 +34713,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ162">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR162">
         <v>1.47</v>
@@ -35032,7 +35044,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35522,7 +35534,7 @@
         <v>0.71</v>
       </c>
       <c r="AP166">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ166">
         <v>0.73</v>
@@ -35650,7 +35662,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36062,7 +36074,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36143,7 +36155,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ169">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR169">
         <v>1.71</v>
@@ -36680,7 +36692,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37170,10 +37182,10 @@
         <v>0.14</v>
       </c>
       <c r="AP174">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ174">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR174">
         <v>1.76</v>
@@ -37298,7 +37310,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37582,10 +37594,10 @@
         <v>0.83</v>
       </c>
       <c r="AP176">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ176">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR176">
         <v>1.6</v>
@@ -37710,7 +37722,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -37791,7 +37803,7 @@
         <v>2</v>
       </c>
       <c r="AQ177">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR177">
         <v>1.68</v>
@@ -37994,7 +38006,7 @@
         <v>1</v>
       </c>
       <c r="AP178">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ178">
         <v>1.08</v>
@@ -38122,7 +38134,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38200,7 +38212,7 @@
         <v>2</v>
       </c>
       <c r="AP179">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ179">
         <v>1.36</v>
@@ -38328,7 +38340,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38409,7 +38421,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ180">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR180">
         <v>1.48</v>
@@ -38612,7 +38624,7 @@
         <v>1.14</v>
       </c>
       <c r="AP181">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ181">
         <v>1.27</v>
@@ -39024,7 +39036,7 @@
         <v>0.88</v>
       </c>
       <c r="AP183">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ183">
         <v>1</v>
@@ -39152,7 +39164,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39439,7 +39451,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ185">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR185">
         <v>1.42</v>
@@ -39645,7 +39657,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ186">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR186">
         <v>1.44</v>
@@ -39976,7 +39988,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40594,7 +40606,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40800,7 +40812,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41006,7 +41018,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41212,7 +41224,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -41702,7 +41714,7 @@
         <v>0.63</v>
       </c>
       <c r="AP196">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ196">
         <v>0.55</v>
@@ -41911,7 +41923,7 @@
         <v>2</v>
       </c>
       <c r="AQ197">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR197">
         <v>1.63</v>
@@ -42320,7 +42332,7 @@
         <v>1.38</v>
       </c>
       <c r="AP199">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ199">
         <v>1.27</v>
@@ -42448,7 +42460,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42529,7 +42541,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ200">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR200">
         <v>1.61</v>
@@ -42860,7 +42872,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -42938,7 +42950,7 @@
         <v>0.67</v>
       </c>
       <c r="AP202">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ202">
         <v>0.58</v>
@@ -43066,7 +43078,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43684,7 +43696,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -43765,7 +43777,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ206">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR206">
         <v>1.42</v>
@@ -43968,7 +43980,7 @@
         <v>0.78</v>
       </c>
       <c r="AP207">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ207">
         <v>1</v>
@@ -44096,7 +44108,7 @@
         <v>94</v>
       </c>
       <c r="P208" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44174,10 +44186,10 @@
         <v>1.11</v>
       </c>
       <c r="AP208">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ208">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR208">
         <v>1.46</v>
@@ -44714,7 +44726,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -44920,7 +44932,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -44998,7 +45010,7 @@
         <v>1.1</v>
       </c>
       <c r="AP212">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ212">
         <v>1.42</v>
@@ -45126,7 +45138,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45332,7 +45344,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45744,7 +45756,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46443,7 +46455,7 @@
         <v>2</v>
       </c>
       <c r="AQ219">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR219">
         <v>1.15</v>
@@ -46980,7 +46992,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47061,7 +47073,7 @@
         <v>2</v>
       </c>
       <c r="AQ222">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AR222">
         <v>1.64</v>
@@ -47264,10 +47276,10 @@
         <v>1.11</v>
       </c>
       <c r="AP223">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AQ223">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR223">
         <v>1.71</v>
@@ -47392,7 +47404,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47676,10 +47688,10 @@
         <v>0.2</v>
       </c>
       <c r="AP225">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ225">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AR225">
         <v>1.43</v>
@@ -47804,7 +47816,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -47882,7 +47894,7 @@
         <v>1.11</v>
       </c>
       <c r="AP226">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AQ226">
         <v>1.27</v>
@@ -48010,7 +48022,7 @@
         <v>200</v>
       </c>
       <c r="P227" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q227">
         <v>2.25</v>
@@ -48088,7 +48100,7 @@
         <v>1</v>
       </c>
       <c r="AP227">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ227">
         <v>1.18</v>
@@ -48294,7 +48306,7 @@
         <v>0.5</v>
       </c>
       <c r="AP228">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AQ228">
         <v>0.55</v>
@@ -48422,7 +48434,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48628,7 +48640,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48709,7 +48721,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ230">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR230">
         <v>1.54</v>
@@ -48834,7 +48846,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49658,7 +49670,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50151,7 +50163,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ237">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AR237">
         <v>1.37</v>
@@ -50482,7 +50494,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51100,7 +51112,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51512,7 +51524,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51718,7 +51730,7 @@
         <v>188</v>
       </c>
       <c r="P245" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q245">
         <v>2.63</v>
@@ -51924,7 +51936,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52287,6 +52299,1036 @@
       </c>
       <c r="BP247">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="248" spans="1:68">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>7728442</v>
+      </c>
+      <c r="C248" t="s">
+        <v>68</v>
+      </c>
+      <c r="D248" t="s">
+        <v>69</v>
+      </c>
+      <c r="E248" s="2">
+        <v>45676.41666666666</v>
+      </c>
+      <c r="F248">
+        <v>23</v>
+      </c>
+      <c r="G248" t="s">
+        <v>78</v>
+      </c>
+      <c r="H248" t="s">
+        <v>75</v>
+      </c>
+      <c r="I248">
+        <v>0</v>
+      </c>
+      <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248">
+        <v>0</v>
+      </c>
+      <c r="L248">
+        <v>0</v>
+      </c>
+      <c r="M248">
+        <v>1</v>
+      </c>
+      <c r="N248">
+        <v>1</v>
+      </c>
+      <c r="O248" t="s">
+        <v>94</v>
+      </c>
+      <c r="P248" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q248">
+        <v>3.25</v>
+      </c>
+      <c r="R248">
+        <v>2</v>
+      </c>
+      <c r="S248">
+        <v>3.6</v>
+      </c>
+      <c r="T248">
+        <v>1.5</v>
+      </c>
+      <c r="U248">
+        <v>2.5</v>
+      </c>
+      <c r="V248">
+        <v>3.4</v>
+      </c>
+      <c r="W248">
+        <v>1.3</v>
+      </c>
+      <c r="X248">
+        <v>10</v>
+      </c>
+      <c r="Y248">
+        <v>1.06</v>
+      </c>
+      <c r="Z248">
+        <v>2.45</v>
+      </c>
+      <c r="AA248">
+        <v>3</v>
+      </c>
+      <c r="AB248">
+        <v>3</v>
+      </c>
+      <c r="AC248">
+        <v>1.09</v>
+      </c>
+      <c r="AD248">
+        <v>7</v>
+      </c>
+      <c r="AE248">
+        <v>1.42</v>
+      </c>
+      <c r="AF248">
+        <v>2.8</v>
+      </c>
+      <c r="AG248">
+        <v>2.34</v>
+      </c>
+      <c r="AH248">
+        <v>1.53</v>
+      </c>
+      <c r="AI248">
+        <v>1.83</v>
+      </c>
+      <c r="AJ248">
+        <v>1.83</v>
+      </c>
+      <c r="AK248">
+        <v>1.38</v>
+      </c>
+      <c r="AL248">
+        <v>1.33</v>
+      </c>
+      <c r="AM248">
+        <v>1.53</v>
+      </c>
+      <c r="AN248">
+        <v>1.64</v>
+      </c>
+      <c r="AO248">
+        <v>1.2</v>
+      </c>
+      <c r="AP248">
+        <v>1.5</v>
+      </c>
+      <c r="AQ248">
+        <v>1.36</v>
+      </c>
+      <c r="AR248">
+        <v>1.41</v>
+      </c>
+      <c r="AS248">
+        <v>1.41</v>
+      </c>
+      <c r="AT248">
+        <v>2.82</v>
+      </c>
+      <c r="AU248">
+        <v>5</v>
+      </c>
+      <c r="AV248">
+        <v>4</v>
+      </c>
+      <c r="AW248">
+        <v>10</v>
+      </c>
+      <c r="AX248">
+        <v>4</v>
+      </c>
+      <c r="AY248">
+        <v>16</v>
+      </c>
+      <c r="AZ248">
+        <v>9</v>
+      </c>
+      <c r="BA248">
+        <v>5</v>
+      </c>
+      <c r="BB248">
+        <v>1</v>
+      </c>
+      <c r="BC248">
+        <v>6</v>
+      </c>
+      <c r="BD248">
+        <v>1.7</v>
+      </c>
+      <c r="BE248">
+        <v>6.75</v>
+      </c>
+      <c r="BF248">
+        <v>2.4</v>
+      </c>
+      <c r="BG248">
+        <v>1.3</v>
+      </c>
+      <c r="BH248">
+        <v>3.1</v>
+      </c>
+      <c r="BI248">
+        <v>1.52</v>
+      </c>
+      <c r="BJ248">
+        <v>2.3</v>
+      </c>
+      <c r="BK248">
+        <v>1.85</v>
+      </c>
+      <c r="BL248">
+        <v>1.81</v>
+      </c>
+      <c r="BM248">
+        <v>2.32</v>
+      </c>
+      <c r="BN248">
+        <v>1.52</v>
+      </c>
+      <c r="BO248">
+        <v>3</v>
+      </c>
+      <c r="BP248">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="249" spans="1:68">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>7728448</v>
+      </c>
+      <c r="C249" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249" s="2">
+        <v>45676.51041666666</v>
+      </c>
+      <c r="F249">
+        <v>23</v>
+      </c>
+      <c r="G249" t="s">
+        <v>77</v>
+      </c>
+      <c r="H249" t="s">
+        <v>74</v>
+      </c>
+      <c r="I249">
+        <v>3</v>
+      </c>
+      <c r="J249">
+        <v>0</v>
+      </c>
+      <c r="K249">
+        <v>3</v>
+      </c>
+      <c r="L249">
+        <v>6</v>
+      </c>
+      <c r="M249">
+        <v>0</v>
+      </c>
+      <c r="N249">
+        <v>6</v>
+      </c>
+      <c r="O249" t="s">
+        <v>250</v>
+      </c>
+      <c r="P249" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q249">
+        <v>2</v>
+      </c>
+      <c r="R249">
+        <v>2.3</v>
+      </c>
+      <c r="S249">
+        <v>5.5</v>
+      </c>
+      <c r="T249">
+        <v>1.35</v>
+      </c>
+      <c r="U249">
+        <v>2.95</v>
+      </c>
+      <c r="V249">
+        <v>2.65</v>
+      </c>
+      <c r="W249">
+        <v>1.42</v>
+      </c>
+      <c r="X249">
+        <v>6.45</v>
+      </c>
+      <c r="Y249">
+        <v>1.09</v>
+      </c>
+      <c r="Z249">
+        <v>1.63</v>
+      </c>
+      <c r="AA249">
+        <v>3.92</v>
+      </c>
+      <c r="AB249">
+        <v>5.45</v>
+      </c>
+      <c r="AC249">
+        <v>1.05</v>
+      </c>
+      <c r="AD249">
+        <v>9.5</v>
+      </c>
+      <c r="AE249">
+        <v>1.25</v>
+      </c>
+      <c r="AF249">
+        <v>3.75</v>
+      </c>
+      <c r="AG249">
+        <v>1.99</v>
+      </c>
+      <c r="AH249">
+        <v>1.82</v>
+      </c>
+      <c r="AI249">
+        <v>1.9</v>
+      </c>
+      <c r="AJ249">
+        <v>1.85</v>
+      </c>
+      <c r="AK249">
+        <v>1.08</v>
+      </c>
+      <c r="AL249">
+        <v>1.17</v>
+      </c>
+      <c r="AM249">
+        <v>2.5</v>
+      </c>
+      <c r="AN249">
+        <v>1.45</v>
+      </c>
+      <c r="AO249">
+        <v>1</v>
+      </c>
+      <c r="AP249">
+        <v>1.58</v>
+      </c>
+      <c r="AQ249">
+        <v>0.91</v>
+      </c>
+      <c r="AR249">
+        <v>1.51</v>
+      </c>
+      <c r="AS249">
+        <v>0.87</v>
+      </c>
+      <c r="AT249">
+        <v>2.38</v>
+      </c>
+      <c r="AU249">
+        <v>10</v>
+      </c>
+      <c r="AV249">
+        <v>3</v>
+      </c>
+      <c r="AW249">
+        <v>10</v>
+      </c>
+      <c r="AX249">
+        <v>4</v>
+      </c>
+      <c r="AY249">
+        <v>21</v>
+      </c>
+      <c r="AZ249">
+        <v>7</v>
+      </c>
+      <c r="BA249">
+        <v>4</v>
+      </c>
+      <c r="BB249">
+        <v>1</v>
+      </c>
+      <c r="BC249">
+        <v>5</v>
+      </c>
+      <c r="BD249">
+        <v>1.36</v>
+      </c>
+      <c r="BE249">
+        <v>7</v>
+      </c>
+      <c r="BF249">
+        <v>3.45</v>
+      </c>
+      <c r="BG249">
+        <v>1.29</v>
+      </c>
+      <c r="BH249">
+        <v>3.15</v>
+      </c>
+      <c r="BI249">
+        <v>1.5</v>
+      </c>
+      <c r="BJ249">
+        <v>2.35</v>
+      </c>
+      <c r="BK249">
+        <v>1.81</v>
+      </c>
+      <c r="BL249">
+        <v>1.85</v>
+      </c>
+      <c r="BM249">
+        <v>2.25</v>
+      </c>
+      <c r="BN249">
+        <v>1.53</v>
+      </c>
+      <c r="BO249">
+        <v>2.9</v>
+      </c>
+      <c r="BP249">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="250" spans="1:68">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>7728451</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250" t="s">
+        <v>69</v>
+      </c>
+      <c r="E250" s="2">
+        <v>45676.60416666666</v>
+      </c>
+      <c r="F250">
+        <v>23</v>
+      </c>
+      <c r="G250" t="s">
+        <v>91</v>
+      </c>
+      <c r="H250" t="s">
+        <v>84</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>1</v>
+      </c>
+      <c r="K250">
+        <v>1</v>
+      </c>
+      <c r="L250">
+        <v>2</v>
+      </c>
+      <c r="M250">
+        <v>2</v>
+      </c>
+      <c r="N250">
+        <v>4</v>
+      </c>
+      <c r="O250" t="s">
+        <v>251</v>
+      </c>
+      <c r="P250" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q250">
+        <v>2.4</v>
+      </c>
+      <c r="R250">
+        <v>1.95</v>
+      </c>
+      <c r="S250">
+        <v>5.25</v>
+      </c>
+      <c r="T250">
+        <v>1.53</v>
+      </c>
+      <c r="U250">
+        <v>2.35</v>
+      </c>
+      <c r="V250">
+        <v>3.4</v>
+      </c>
+      <c r="W250">
+        <v>1.28</v>
+      </c>
+      <c r="X250">
+        <v>8.5</v>
+      </c>
+      <c r="Y250">
+        <v>1.04</v>
+      </c>
+      <c r="Z250">
+        <v>1.75</v>
+      </c>
+      <c r="AA250">
+        <v>3.48</v>
+      </c>
+      <c r="AB250">
+        <v>5.15</v>
+      </c>
+      <c r="AC250">
+        <v>1.11</v>
+      </c>
+      <c r="AD250">
+        <v>6.25</v>
+      </c>
+      <c r="AE250">
+        <v>1.5</v>
+      </c>
+      <c r="AF250">
+        <v>2.55</v>
+      </c>
+      <c r="AG250">
+        <v>2.3</v>
+      </c>
+      <c r="AH250">
+        <v>1.5</v>
+      </c>
+      <c r="AI250">
+        <v>2.15</v>
+      </c>
+      <c r="AJ250">
+        <v>1.6</v>
+      </c>
+      <c r="AK250">
+        <v>1.15</v>
+      </c>
+      <c r="AL250">
+        <v>1.3</v>
+      </c>
+      <c r="AM250">
+        <v>1.95</v>
+      </c>
+      <c r="AN250">
+        <v>1.3</v>
+      </c>
+      <c r="AO250">
+        <v>0.18</v>
+      </c>
+      <c r="AP250">
+        <v>1.27</v>
+      </c>
+      <c r="AQ250">
+        <v>0.25</v>
+      </c>
+      <c r="AR250">
+        <v>1.68</v>
+      </c>
+      <c r="AS250">
+        <v>1</v>
+      </c>
+      <c r="AT250">
+        <v>2.68</v>
+      </c>
+      <c r="AU250">
+        <v>5</v>
+      </c>
+      <c r="AV250">
+        <v>5</v>
+      </c>
+      <c r="AW250">
+        <v>5</v>
+      </c>
+      <c r="AX250">
+        <v>9</v>
+      </c>
+      <c r="AY250">
+        <v>14</v>
+      </c>
+      <c r="AZ250">
+        <v>17</v>
+      </c>
+      <c r="BA250">
+        <v>5</v>
+      </c>
+      <c r="BB250">
+        <v>3</v>
+      </c>
+      <c r="BC250">
+        <v>8</v>
+      </c>
+      <c r="BD250">
+        <v>1.31</v>
+      </c>
+      <c r="BE250">
+        <v>12.5</v>
+      </c>
+      <c r="BF250">
+        <v>4.14</v>
+      </c>
+      <c r="BG250">
+        <v>1.33</v>
+      </c>
+      <c r="BH250">
+        <v>2.83</v>
+      </c>
+      <c r="BI250">
+        <v>1.62</v>
+      </c>
+      <c r="BJ250">
+        <v>2.1</v>
+      </c>
+      <c r="BK250">
+        <v>2.08</v>
+      </c>
+      <c r="BL250">
+        <v>1.67</v>
+      </c>
+      <c r="BM250">
+        <v>2.71</v>
+      </c>
+      <c r="BN250">
+        <v>1.38</v>
+      </c>
+      <c r="BO250">
+        <v>3.74</v>
+      </c>
+      <c r="BP250">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="251" spans="1:68">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>7728444</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>69</v>
+      </c>
+      <c r="E251" s="2">
+        <v>45676.60416666666</v>
+      </c>
+      <c r="F251">
+        <v>23</v>
+      </c>
+      <c r="G251" t="s">
+        <v>86</v>
+      </c>
+      <c r="H251" t="s">
+        <v>88</v>
+      </c>
+      <c r="I251">
+        <v>1</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251">
+        <v>1</v>
+      </c>
+      <c r="L251">
+        <v>1</v>
+      </c>
+      <c r="M251">
+        <v>2</v>
+      </c>
+      <c r="N251">
+        <v>3</v>
+      </c>
+      <c r="O251" t="s">
+        <v>124</v>
+      </c>
+      <c r="P251" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q251">
+        <v>2.4</v>
+      </c>
+      <c r="R251">
+        <v>2.25</v>
+      </c>
+      <c r="S251">
+        <v>4</v>
+      </c>
+      <c r="T251">
+        <v>1.32</v>
+      </c>
+      <c r="U251">
+        <v>3.15</v>
+      </c>
+      <c r="V251">
+        <v>2.4</v>
+      </c>
+      <c r="W251">
+        <v>1.51</v>
+      </c>
+      <c r="X251">
+        <v>5.45</v>
+      </c>
+      <c r="Y251">
+        <v>1.12</v>
+      </c>
+      <c r="Z251">
+        <v>1.91</v>
+      </c>
+      <c r="AA251">
+        <v>3.6</v>
+      </c>
+      <c r="AB251">
+        <v>3.7</v>
+      </c>
+      <c r="AC251">
+        <v>1.04</v>
+      </c>
+      <c r="AD251">
+        <v>10</v>
+      </c>
+      <c r="AE251">
+        <v>1.2</v>
+      </c>
+      <c r="AF251">
+        <v>4.33</v>
+      </c>
+      <c r="AG251">
+        <v>1.61</v>
+      </c>
+      <c r="AH251">
+        <v>2.1</v>
+      </c>
+      <c r="AI251">
+        <v>1.57</v>
+      </c>
+      <c r="AJ251">
+        <v>2.3</v>
+      </c>
+      <c r="AK251">
+        <v>1.2</v>
+      </c>
+      <c r="AL251">
+        <v>1.2</v>
+      </c>
+      <c r="AM251">
+        <v>1.9</v>
+      </c>
+      <c r="AN251">
+        <v>1.27</v>
+      </c>
+      <c r="AO251">
+        <v>0.45</v>
+      </c>
+      <c r="AP251">
+        <v>1.17</v>
+      </c>
+      <c r="AQ251">
+        <v>0.67</v>
+      </c>
+      <c r="AR251">
+        <v>1.68</v>
+      </c>
+      <c r="AS251">
+        <v>1.32</v>
+      </c>
+      <c r="AT251">
+        <v>3</v>
+      </c>
+      <c r="AU251">
+        <v>7</v>
+      </c>
+      <c r="AV251">
+        <v>5</v>
+      </c>
+      <c r="AW251">
+        <v>9</v>
+      </c>
+      <c r="AX251">
+        <v>5</v>
+      </c>
+      <c r="AY251">
+        <v>18</v>
+      </c>
+      <c r="AZ251">
+        <v>10</v>
+      </c>
+      <c r="BA251">
+        <v>3</v>
+      </c>
+      <c r="BB251">
+        <v>4</v>
+      </c>
+      <c r="BC251">
+        <v>7</v>
+      </c>
+      <c r="BD251">
+        <v>1.84</v>
+      </c>
+      <c r="BE251">
+        <v>6.4</v>
+      </c>
+      <c r="BF251">
+        <v>2.59</v>
+      </c>
+      <c r="BG251">
+        <v>1.31</v>
+      </c>
+      <c r="BH251">
+        <v>2.92</v>
+      </c>
+      <c r="BI251">
+        <v>1.59</v>
+      </c>
+      <c r="BJ251">
+        <v>2.16</v>
+      </c>
+      <c r="BK251">
+        <v>2.03</v>
+      </c>
+      <c r="BL251">
+        <v>1.7</v>
+      </c>
+      <c r="BM251">
+        <v>2.67</v>
+      </c>
+      <c r="BN251">
+        <v>1.39</v>
+      </c>
+      <c r="BO251">
+        <v>3.58</v>
+      </c>
+      <c r="BP251">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7728441</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45676.70833333334</v>
+      </c>
+      <c r="F252">
+        <v>23</v>
+      </c>
+      <c r="G252" t="s">
+        <v>90</v>
+      </c>
+      <c r="H252" t="s">
+        <v>81</v>
+      </c>
+      <c r="I252">
+        <v>0</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252">
+        <v>0</v>
+      </c>
+      <c r="L252">
+        <v>0</v>
+      </c>
+      <c r="M252">
+        <v>0</v>
+      </c>
+      <c r="N252">
+        <v>0</v>
+      </c>
+      <c r="O252" t="s">
+        <v>94</v>
+      </c>
+      <c r="P252" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q252">
+        <v>2.15</v>
+      </c>
+      <c r="R252">
+        <v>2.15</v>
+      </c>
+      <c r="S252">
+        <v>5.5</v>
+      </c>
+      <c r="T252">
+        <v>1.44</v>
+      </c>
+      <c r="U252">
+        <v>2.6</v>
+      </c>
+      <c r="V252">
+        <v>2.95</v>
+      </c>
+      <c r="W252">
+        <v>1.35</v>
+      </c>
+      <c r="X252">
+        <v>7.9</v>
+      </c>
+      <c r="Y252">
+        <v>1.05</v>
+      </c>
+      <c r="Z252">
+        <v>1.6</v>
+      </c>
+      <c r="AA252">
+        <v>3.8</v>
+      </c>
+      <c r="AB252">
+        <v>5.75</v>
+      </c>
+      <c r="AC252">
+        <v>1.05</v>
+      </c>
+      <c r="AD252">
+        <v>9</v>
+      </c>
+      <c r="AE252">
+        <v>1.33</v>
+      </c>
+      <c r="AF252">
+        <v>3.1</v>
+      </c>
+      <c r="AG252">
+        <v>2.01</v>
+      </c>
+      <c r="AH252">
+        <v>1.81</v>
+      </c>
+      <c r="AI252">
+        <v>2.1</v>
+      </c>
+      <c r="AJ252">
+        <v>1.68</v>
+      </c>
+      <c r="AK252">
+        <v>1.08</v>
+      </c>
+      <c r="AL252">
+        <v>1.2</v>
+      </c>
+      <c r="AM252">
+        <v>2.4</v>
+      </c>
+      <c r="AN252">
+        <v>2.1</v>
+      </c>
+      <c r="AO252">
+        <v>1.27</v>
+      </c>
+      <c r="AP252">
+        <v>2</v>
+      </c>
+      <c r="AQ252">
+        <v>1.25</v>
+      </c>
+      <c r="AR252">
+        <v>1.71</v>
+      </c>
+      <c r="AS252">
+        <v>1.11</v>
+      </c>
+      <c r="AT252">
+        <v>2.82</v>
+      </c>
+      <c r="AU252">
+        <v>10</v>
+      </c>
+      <c r="AV252">
+        <v>2</v>
+      </c>
+      <c r="AW252">
+        <v>15</v>
+      </c>
+      <c r="AX252">
+        <v>2</v>
+      </c>
+      <c r="AY252">
+        <v>30</v>
+      </c>
+      <c r="AZ252">
+        <v>4</v>
+      </c>
+      <c r="BA252">
+        <v>10</v>
+      </c>
+      <c r="BB252">
+        <v>4</v>
+      </c>
+      <c r="BC252">
+        <v>14</v>
+      </c>
+      <c r="BD252">
+        <v>1.3</v>
+      </c>
+      <c r="BE252">
+        <v>12.5</v>
+      </c>
+      <c r="BF252">
+        <v>4.24</v>
+      </c>
+      <c r="BG252">
+        <v>1.34</v>
+      </c>
+      <c r="BH252">
+        <v>2.78</v>
+      </c>
+      <c r="BI252">
+        <v>1.64</v>
+      </c>
+      <c r="BJ252">
+        <v>2.07</v>
+      </c>
+      <c r="BK252">
+        <v>2.11</v>
+      </c>
+      <c r="BL252">
+        <v>1.65</v>
+      </c>
+      <c r="BM252">
+        <v>2.78</v>
+      </c>
+      <c r="BN252">
+        <v>1.36</v>
+      </c>
+      <c r="BO252">
+        <v>3.8</v>
+      </c>
+      <c r="BP252">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="349">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -772,6 +772,9 @@
     <t>['77', '78']</t>
   </si>
   <si>
+    <t>['57', '61', '90+3']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1055,6 +1058,9 @@
   </si>
   <si>
     <t>['50', '90+6']</t>
+  </si>
+  <si>
+    <t>['40', '71']</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP252"/>
+  <dimension ref="A1:BP253"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1672,7 +1678,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -1956,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ3">
         <v>0.67</v>
@@ -2084,7 +2090,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2577,7 +2583,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ6">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2702,7 +2708,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2908,7 +2914,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3114,7 +3120,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3938,7 +3944,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4144,7 +4150,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -5174,7 +5180,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5792,7 +5798,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -5998,7 +6004,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6204,7 +6210,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6410,7 +6416,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6616,7 +6622,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6822,7 +6828,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7234,7 +7240,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7724,7 +7730,7 @@
         <v>3</v>
       </c>
       <c r="AP31">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ31">
         <v>1.33</v>
@@ -7852,7 +7858,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8058,7 +8064,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8470,7 +8476,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -9088,7 +9094,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -9375,7 +9381,7 @@
         <v>2</v>
       </c>
       <c r="AQ39">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR39">
         <v>1.32</v>
@@ -10324,7 +10330,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10942,7 +10948,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -11844,7 +11850,7 @@
         <v>1.5</v>
       </c>
       <c r="AP51">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ51">
         <v>1.08</v>
@@ -12590,7 +12596,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12796,7 +12802,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13002,7 +13008,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13083,7 +13089,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ57">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR57">
         <v>1.77</v>
@@ -13208,7 +13214,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13620,7 +13626,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14238,7 +14244,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14856,7 +14862,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -15268,7 +15274,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15474,7 +15480,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -15758,7 +15764,7 @@
         <v>2</v>
       </c>
       <c r="AP70">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ70">
         <v>1.25</v>
@@ -16092,7 +16098,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16298,7 +16304,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16504,7 +16510,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17328,7 +17334,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17534,7 +17540,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17946,7 +17952,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18024,7 +18030,7 @@
         <v>1.67</v>
       </c>
       <c r="AP81">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ81">
         <v>1.36</v>
@@ -18152,7 +18158,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18358,7 +18364,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19057,7 +19063,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR86">
         <v>1.47</v>
@@ -19182,7 +19188,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19594,7 +19600,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19800,7 +19806,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20212,7 +20218,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20293,7 +20299,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR92">
         <v>1.42</v>
@@ -20624,7 +20630,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20830,7 +20836,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21860,7 +21866,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23174,7 +23180,7 @@
         <v>1.25</v>
       </c>
       <c r="AP106">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ106">
         <v>0.73</v>
@@ -23302,7 +23308,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23920,7 +23926,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24332,7 +24338,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24538,7 +24544,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24950,7 +24956,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25774,7 +25780,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26267,7 +26273,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ121">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR121">
         <v>1.32</v>
@@ -26392,7 +26398,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26804,7 +26810,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -26882,7 +26888,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ124">
         <v>0.58</v>
@@ -27216,7 +27222,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27628,7 +27634,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -28040,7 +28046,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28246,7 +28252,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28452,7 +28458,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28864,7 +28870,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29070,7 +29076,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29688,7 +29694,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30306,7 +30312,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30512,7 +30518,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30590,7 +30596,7 @@
         <v>1.17</v>
       </c>
       <c r="AP142">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ142">
         <v>1.18</v>
@@ -30718,7 +30724,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30924,7 +30930,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31336,7 +31342,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31748,7 +31754,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32778,7 +32784,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33396,7 +33402,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -34507,7 +34513,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ161">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR161">
         <v>1.62</v>
@@ -35044,7 +35050,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35662,7 +35668,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36074,7 +36080,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36564,7 +36570,7 @@
         <v>0.71</v>
       </c>
       <c r="AP171">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ171">
         <v>0.55</v>
@@ -36692,7 +36698,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37310,7 +37316,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37391,7 +37397,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ175">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR175">
         <v>1.58</v>
@@ -37722,7 +37728,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38134,7 +38140,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38340,7 +38346,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39039,7 +39045,7 @@
         <v>1.17</v>
       </c>
       <c r="AQ183">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR183">
         <v>1.63</v>
@@ -39164,7 +39170,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39988,7 +39994,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40066,7 +40072,7 @@
         <v>1.38</v>
       </c>
       <c r="AP188">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ188">
         <v>1.33</v>
@@ -40606,7 +40612,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40812,7 +40818,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -41018,7 +41024,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41224,7 +41230,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42460,7 +42466,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42872,7 +42878,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43078,7 +43084,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43696,7 +43702,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -43983,7 +43989,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ207">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR207">
         <v>1.45</v>
@@ -44108,7 +44114,7 @@
         <v>94</v>
       </c>
       <c r="P208" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44726,7 +44732,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -44932,7 +44938,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45138,7 +45144,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45344,7 +45350,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45422,7 +45428,7 @@
         <v>1.11</v>
       </c>
       <c r="AP214">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ214">
         <v>1.09</v>
@@ -45756,7 +45762,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46992,7 +46998,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47404,7 +47410,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47485,7 +47491,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ224">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR224">
         <v>1.5</v>
@@ -47816,7 +47822,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48022,7 +48028,7 @@
         <v>200</v>
       </c>
       <c r="P227" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q227">
         <v>2.25</v>
@@ -48434,7 +48440,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48640,7 +48646,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48846,7 +48852,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49670,7 +49676,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50494,7 +50500,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -51112,7 +51118,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51524,7 +51530,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51730,7 +51736,7 @@
         <v>188</v>
       </c>
       <c r="P245" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q245">
         <v>2.63</v>
@@ -51936,7 +51942,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52760,7 +52766,7 @@
         <v>251</v>
       </c>
       <c r="P250" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -52966,7 +52972,7 @@
         <v>124</v>
       </c>
       <c r="P251" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53329,6 +53335,212 @@
       </c>
       <c r="BP252">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="253" spans="1:68">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>7728450</v>
+      </c>
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="2">
+        <v>45677.6875</v>
+      </c>
+      <c r="F253">
+        <v>23</v>
+      </c>
+      <c r="G253" t="s">
+        <v>71</v>
+      </c>
+      <c r="H253" t="s">
+        <v>83</v>
+      </c>
+      <c r="I253">
+        <v>0</v>
+      </c>
+      <c r="J253">
+        <v>1</v>
+      </c>
+      <c r="K253">
+        <v>1</v>
+      </c>
+      <c r="L253">
+        <v>3</v>
+      </c>
+      <c r="M253">
+        <v>2</v>
+      </c>
+      <c r="N253">
+        <v>5</v>
+      </c>
+      <c r="O253" t="s">
+        <v>252</v>
+      </c>
+      <c r="P253" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q253">
+        <v>2.88</v>
+      </c>
+      <c r="R253">
+        <v>1.83</v>
+      </c>
+      <c r="S253">
+        <v>5</v>
+      </c>
+      <c r="T253">
+        <v>1.62</v>
+      </c>
+      <c r="U253">
+        <v>2.2</v>
+      </c>
+      <c r="V253">
+        <v>4</v>
+      </c>
+      <c r="W253">
+        <v>1.22</v>
+      </c>
+      <c r="X253">
+        <v>13</v>
+      </c>
+      <c r="Y253">
+        <v>1.04</v>
+      </c>
+      <c r="Z253">
+        <v>2.1</v>
+      </c>
+      <c r="AA253">
+        <v>2.88</v>
+      </c>
+      <c r="AB253">
+        <v>3.75</v>
+      </c>
+      <c r="AC253">
+        <v>1.12</v>
+      </c>
+      <c r="AD253">
+        <v>6</v>
+      </c>
+      <c r="AE253">
+        <v>1.57</v>
+      </c>
+      <c r="AF253">
+        <v>2.25</v>
+      </c>
+      <c r="AG253">
+        <v>2.75</v>
+      </c>
+      <c r="AH253">
+        <v>1.4</v>
+      </c>
+      <c r="AI253">
+        <v>2.38</v>
+      </c>
+      <c r="AJ253">
+        <v>1.53</v>
+      </c>
+      <c r="AK253">
+        <v>1.22</v>
+      </c>
+      <c r="AL253">
+        <v>1.33</v>
+      </c>
+      <c r="AM253">
+        <v>1.72</v>
+      </c>
+      <c r="AN253">
+        <v>2.18</v>
+      </c>
+      <c r="AO253">
+        <v>1</v>
+      </c>
+      <c r="AP253">
+        <v>2.25</v>
+      </c>
+      <c r="AQ253">
+        <v>0.92</v>
+      </c>
+      <c r="AR253">
+        <v>1.15</v>
+      </c>
+      <c r="AS253">
+        <v>1.08</v>
+      </c>
+      <c r="AT253">
+        <v>2.23</v>
+      </c>
+      <c r="AU253">
+        <v>8</v>
+      </c>
+      <c r="AV253">
+        <v>5</v>
+      </c>
+      <c r="AW253">
+        <v>10</v>
+      </c>
+      <c r="AX253">
+        <v>4</v>
+      </c>
+      <c r="AY253">
+        <v>20</v>
+      </c>
+      <c r="AZ253">
+        <v>10</v>
+      </c>
+      <c r="BA253">
+        <v>8</v>
+      </c>
+      <c r="BB253">
+        <v>1</v>
+      </c>
+      <c r="BC253">
+        <v>9</v>
+      </c>
+      <c r="BD253">
+        <v>1.6</v>
+      </c>
+      <c r="BE253">
+        <v>6.65</v>
+      </c>
+      <c r="BF253">
+        <v>3.22</v>
+      </c>
+      <c r="BG253">
+        <v>1.36</v>
+      </c>
+      <c r="BH253">
+        <v>2.79</v>
+      </c>
+      <c r="BI253">
+        <v>1.67</v>
+      </c>
+      <c r="BJ253">
+        <v>2.08</v>
+      </c>
+      <c r="BK253">
+        <v>2.11</v>
+      </c>
+      <c r="BL253">
+        <v>1.62</v>
+      </c>
+      <c r="BM253">
+        <v>2.78</v>
+      </c>
+      <c r="BN253">
+        <v>1.34</v>
+      </c>
+      <c r="BO253">
+        <v>3.92</v>
+      </c>
+      <c r="BP253">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2024)/Spain Segunda División_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="350">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -775,6 +775,9 @@
     <t>['57', '61', '90+3']</t>
   </si>
   <si>
+    <t>['45', '74']</t>
+  </si>
+  <si>
     <t>['42', '45+3']</t>
   </si>
   <si>
@@ -1422,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP253"/>
+  <dimension ref="A1:BP254"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1678,7 +1681,7 @@
         <v>92</v>
       </c>
       <c r="P2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q2">
         <v>2.6</v>
@@ -2090,7 +2093,7 @@
         <v>94</v>
       </c>
       <c r="P4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q4">
         <v>2.75</v>
@@ -2708,7 +2711,7 @@
         <v>94</v>
       </c>
       <c r="P7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q7">
         <v>3.2</v>
@@ -2914,7 +2917,7 @@
         <v>97</v>
       </c>
       <c r="P8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q8">
         <v>2.75</v>
@@ -3120,7 +3123,7 @@
         <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q9">
         <v>3.4</v>
@@ -3610,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ11">
         <v>1.25</v>
@@ -3944,7 +3947,7 @@
         <v>101</v>
       </c>
       <c r="P13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q13">
         <v>3.03</v>
@@ -4025,7 +4028,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ13">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR13">
         <v>1.32</v>
@@ -4150,7 +4153,7 @@
         <v>102</v>
       </c>
       <c r="P14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q14">
         <v>3</v>
@@ -5180,7 +5183,7 @@
         <v>94</v>
       </c>
       <c r="P19" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q19">
         <v>3.5</v>
@@ -5798,7 +5801,7 @@
         <v>106</v>
       </c>
       <c r="P22" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q22">
         <v>4</v>
@@ -6004,7 +6007,7 @@
         <v>107</v>
       </c>
       <c r="P23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q23">
         <v>2.88</v>
@@ -6210,7 +6213,7 @@
         <v>97</v>
       </c>
       <c r="P24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q24">
         <v>2.75</v>
@@ -6416,7 +6419,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q25">
         <v>2.75</v>
@@ -6622,7 +6625,7 @@
         <v>109</v>
       </c>
       <c r="P26" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q26">
         <v>2.5</v>
@@ -6828,7 +6831,7 @@
         <v>110</v>
       </c>
       <c r="P27" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q27">
         <v>3</v>
@@ -7240,7 +7243,7 @@
         <v>94</v>
       </c>
       <c r="P29" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q29">
         <v>3.25</v>
@@ -7858,7 +7861,7 @@
         <v>92</v>
       </c>
       <c r="P32" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q32">
         <v>2.75</v>
@@ -8064,7 +8067,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q33">
         <v>2.63</v>
@@ -8348,7 +8351,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ34">
         <v>0.67</v>
@@ -8476,7 +8479,7 @@
         <v>94</v>
       </c>
       <c r="P35" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -9094,7 +9097,7 @@
         <v>116</v>
       </c>
       <c r="P38" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q38">
         <v>3</v>
@@ -10330,7 +10333,7 @@
         <v>119</v>
       </c>
       <c r="P44" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q44">
         <v>2.88</v>
@@ -10617,7 +10620,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ45">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR45">
         <v>0.96</v>
@@ -10948,7 +10951,7 @@
         <v>121</v>
       </c>
       <c r="P47" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q47">
         <v>2.4</v>
@@ -12596,7 +12599,7 @@
         <v>126</v>
       </c>
       <c r="P55" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q55">
         <v>2.75</v>
@@ -12674,7 +12677,7 @@
         <v>3</v>
       </c>
       <c r="AP55">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ55">
         <v>1.36</v>
@@ -12802,7 +12805,7 @@
         <v>127</v>
       </c>
       <c r="P56" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q56">
         <v>2.88</v>
@@ -13008,7 +13011,7 @@
         <v>128</v>
       </c>
       <c r="P57" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q57">
         <v>2.6</v>
@@ -13214,7 +13217,7 @@
         <v>129</v>
       </c>
       <c r="P58" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q58">
         <v>3.15</v>
@@ -13626,7 +13629,7 @@
         <v>94</v>
       </c>
       <c r="P60" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -14244,7 +14247,7 @@
         <v>97</v>
       </c>
       <c r="P63" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q63">
         <v>4</v>
@@ -14734,7 +14737,7 @@
         <v>1</v>
       </c>
       <c r="AP65">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ65">
         <v>1.27</v>
@@ -14862,7 +14865,7 @@
         <v>134</v>
       </c>
       <c r="P66" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q66">
         <v>2.75</v>
@@ -14943,7 +14946,7 @@
         <v>2</v>
       </c>
       <c r="AQ66">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR66">
         <v>1.93</v>
@@ -15274,7 +15277,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q68">
         <v>2.88</v>
@@ -15480,7 +15483,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q69">
         <v>2.1</v>
@@ -16098,7 +16101,7 @@
         <v>94</v>
       </c>
       <c r="P72" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q72">
         <v>3.4</v>
@@ -16304,7 +16307,7 @@
         <v>140</v>
       </c>
       <c r="P73" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q73">
         <v>3.1</v>
@@ -16510,7 +16513,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q74">
         <v>2.93</v>
@@ -17209,7 +17212,7 @@
         <v>2</v>
       </c>
       <c r="AQ77">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR77">
         <v>1.33</v>
@@ -17334,7 +17337,7 @@
         <v>145</v>
       </c>
       <c r="P78" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q78">
         <v>2.05</v>
@@ -17540,7 +17543,7 @@
         <v>146</v>
       </c>
       <c r="P79" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q79">
         <v>3.85</v>
@@ -17952,7 +17955,7 @@
         <v>94</v>
       </c>
       <c r="P81" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q81">
         <v>3.55</v>
@@ -18158,7 +18161,7 @@
         <v>148</v>
       </c>
       <c r="P82" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q82">
         <v>2.65</v>
@@ -18364,7 +18367,7 @@
         <v>149</v>
       </c>
       <c r="P83" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q83">
         <v>2.88</v>
@@ -19188,7 +19191,7 @@
         <v>152</v>
       </c>
       <c r="P87" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q87">
         <v>3.25</v>
@@ -19600,7 +19603,7 @@
         <v>153</v>
       </c>
       <c r="P89" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q89">
         <v>2.75</v>
@@ -19806,7 +19809,7 @@
         <v>154</v>
       </c>
       <c r="P90" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q90">
         <v>3.2</v>
@@ -20218,7 +20221,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q92">
         <v>2.38</v>
@@ -20630,7 +20633,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q94">
         <v>3.25</v>
@@ -20836,7 +20839,7 @@
         <v>158</v>
       </c>
       <c r="P95" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q95">
         <v>3</v>
@@ -21738,7 +21741,7 @@
         <v>1</v>
       </c>
       <c r="AP99">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ99">
         <v>1.36</v>
@@ -21866,7 +21869,7 @@
         <v>161</v>
       </c>
       <c r="P100" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q100">
         <v>2.88</v>
@@ -23183,7 +23186,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ106">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR106">
         <v>1.12</v>
@@ -23308,7 +23311,7 @@
         <v>94</v>
       </c>
       <c r="P107" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q107">
         <v>3.4</v>
@@ -23798,7 +23801,7 @@
         <v>1.25</v>
       </c>
       <c r="AP109">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ109">
         <v>1.09</v>
@@ -23926,7 +23929,7 @@
         <v>108</v>
       </c>
       <c r="P110" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q110">
         <v>2.3</v>
@@ -24338,7 +24341,7 @@
         <v>168</v>
       </c>
       <c r="P112" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q112">
         <v>2.45</v>
@@ -24544,7 +24547,7 @@
         <v>169</v>
       </c>
       <c r="P113" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q113">
         <v>2.65</v>
@@ -24956,7 +24959,7 @@
         <v>170</v>
       </c>
       <c r="P115" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q115">
         <v>3.45</v>
@@ -25780,7 +25783,7 @@
         <v>173</v>
       </c>
       <c r="P119" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q119">
         <v>2.8</v>
@@ -26398,7 +26401,7 @@
         <v>175</v>
       </c>
       <c r="P122" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q122">
         <v>2.5</v>
@@ -26810,7 +26813,7 @@
         <v>177</v>
       </c>
       <c r="P124" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q124">
         <v>2.4</v>
@@ -27222,7 +27225,7 @@
         <v>179</v>
       </c>
       <c r="P126" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q126">
         <v>2.63</v>
@@ -27509,7 +27512,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ127">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR127">
         <v>1.1</v>
@@ -27634,7 +27637,7 @@
         <v>137</v>
       </c>
       <c r="P128" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27918,7 +27921,7 @@
         <v>1.4</v>
       </c>
       <c r="AP129">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ129">
         <v>0.82</v>
@@ -28046,7 +28049,7 @@
         <v>180</v>
       </c>
       <c r="P130" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q130">
         <v>3.25</v>
@@ -28252,7 +28255,7 @@
         <v>181</v>
       </c>
       <c r="P131" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q131">
         <v>2.75</v>
@@ -28458,7 +28461,7 @@
         <v>182</v>
       </c>
       <c r="P132" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q132">
         <v>2.88</v>
@@ -28870,7 +28873,7 @@
         <v>94</v>
       </c>
       <c r="P134" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q134">
         <v>3.1</v>
@@ -29076,7 +29079,7 @@
         <v>183</v>
       </c>
       <c r="P135" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q135">
         <v>3.9</v>
@@ -29694,7 +29697,7 @@
         <v>186</v>
       </c>
       <c r="P138" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q138">
         <v>2.4</v>
@@ -30312,7 +30315,7 @@
         <v>188</v>
       </c>
       <c r="P141" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q141">
         <v>2.62</v>
@@ -30390,7 +30393,7 @@
         <v>1.14</v>
       </c>
       <c r="AP141">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ141">
         <v>1.75</v>
@@ -30518,7 +30521,7 @@
         <v>189</v>
       </c>
       <c r="P142" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q142">
         <v>3.6</v>
@@ -30724,7 +30727,7 @@
         <v>190</v>
       </c>
       <c r="P143" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q143">
         <v>3.75</v>
@@ -30930,7 +30933,7 @@
         <v>191</v>
       </c>
       <c r="P144" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q144">
         <v>2.25</v>
@@ -31342,7 +31345,7 @@
         <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q146">
         <v>2.75</v>
@@ -31754,7 +31757,7 @@
         <v>97</v>
       </c>
       <c r="P148" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q148">
         <v>3.65</v>
@@ -32247,7 +32250,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ150">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR150">
         <v>1.6</v>
@@ -32784,7 +32787,7 @@
         <v>197</v>
       </c>
       <c r="P153" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q153">
         <v>2.3</v>
@@ -33402,7 +33405,7 @@
         <v>200</v>
       </c>
       <c r="P156" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q156">
         <v>2.7</v>
@@ -35050,7 +35053,7 @@
         <v>206</v>
       </c>
       <c r="P164" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q164">
         <v>4.75</v>
@@ -35543,7 +35546,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ166">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR166">
         <v>1.42</v>
@@ -35668,7 +35671,7 @@
         <v>208</v>
       </c>
       <c r="P167" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q167">
         <v>3</v>
@@ -36080,7 +36083,7 @@
         <v>209</v>
       </c>
       <c r="P169" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q169">
         <v>2.88</v>
@@ -36698,7 +36701,7 @@
         <v>210</v>
       </c>
       <c r="P172" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -36982,7 +36985,7 @@
         <v>1</v>
       </c>
       <c r="AP173">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ173">
         <v>1.42</v>
@@ -37316,7 +37319,7 @@
         <v>213</v>
       </c>
       <c r="P175" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q175">
         <v>2.3</v>
@@ -37728,7 +37731,7 @@
         <v>94</v>
       </c>
       <c r="P177" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q177">
         <v>2.5</v>
@@ -38140,7 +38143,7 @@
         <v>214</v>
       </c>
       <c r="P179" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q179">
         <v>2.4</v>
@@ -38346,7 +38349,7 @@
         <v>215</v>
       </c>
       <c r="P180" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -39170,7 +39173,7 @@
         <v>217</v>
       </c>
       <c r="P184" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39994,7 +39997,7 @@
         <v>219</v>
       </c>
       <c r="P188" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q188">
         <v>3.5</v>
@@ -40278,7 +40281,7 @@
         <v>1.13</v>
       </c>
       <c r="AP189">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ189">
         <v>1.18</v>
@@ -40612,7 +40615,7 @@
         <v>222</v>
       </c>
       <c r="P191" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q191">
         <v>2.7</v>
@@ -40818,7 +40821,7 @@
         <v>223</v>
       </c>
       <c r="P192" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q192">
         <v>3.2</v>
@@ -40899,7 +40902,7 @@
         <v>2</v>
       </c>
       <c r="AQ192">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR192">
         <v>1.15</v>
@@ -41024,7 +41027,7 @@
         <v>224</v>
       </c>
       <c r="P193" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q193">
         <v>4.33</v>
@@ -41230,7 +41233,7 @@
         <v>108</v>
       </c>
       <c r="P194" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q194">
         <v>3.75</v>
@@ -42466,7 +42469,7 @@
         <v>227</v>
       </c>
       <c r="P200" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q200">
         <v>2.38</v>
@@ -42878,7 +42881,7 @@
         <v>229</v>
       </c>
       <c r="P202" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q202">
         <v>1.95</v>
@@ -43084,7 +43087,7 @@
         <v>230</v>
       </c>
       <c r="P203" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q203">
         <v>3.25</v>
@@ -43702,7 +43705,7 @@
         <v>232</v>
       </c>
       <c r="P206" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q206">
         <v>2.25</v>
@@ -44114,7 +44117,7 @@
         <v>94</v>
       </c>
       <c r="P208" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q208">
         <v>2.3</v>
@@ -44732,7 +44735,7 @@
         <v>234</v>
       </c>
       <c r="P211" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q211">
         <v>2.75</v>
@@ -44813,7 +44816,7 @@
         <v>2</v>
       </c>
       <c r="AQ211">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR211">
         <v>1.69</v>
@@ -44938,7 +44941,7 @@
         <v>235</v>
       </c>
       <c r="P212" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q212">
         <v>3.25</v>
@@ -45144,7 +45147,7 @@
         <v>236</v>
       </c>
       <c r="P213" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q213">
         <v>4.2</v>
@@ -45350,7 +45353,7 @@
         <v>139</v>
       </c>
       <c r="P214" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q214">
         <v>3.6</v>
@@ -45762,7 +45765,7 @@
         <v>238</v>
       </c>
       <c r="P216" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q216">
         <v>2.62</v>
@@ -46046,7 +46049,7 @@
         <v>2.44</v>
       </c>
       <c r="AP217">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ217">
         <v>2.09</v>
@@ -46998,7 +47001,7 @@
         <v>241</v>
       </c>
       <c r="P222" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q222">
         <v>2.25</v>
@@ -47410,7 +47413,7 @@
         <v>117</v>
       </c>
       <c r="P224" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q224">
         <v>2.5</v>
@@ -47822,7 +47825,7 @@
         <v>94</v>
       </c>
       <c r="P226" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q226">
         <v>2.88</v>
@@ -48028,7 +48031,7 @@
         <v>200</v>
       </c>
       <c r="P227" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q227">
         <v>2.25</v>
@@ -48440,7 +48443,7 @@
         <v>94</v>
       </c>
       <c r="P229" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q229">
         <v>2.63</v>
@@ -48646,7 +48649,7 @@
         <v>244</v>
       </c>
       <c r="P230" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q230">
         <v>2.5</v>
@@ -48852,7 +48855,7 @@
         <v>94</v>
       </c>
       <c r="P231" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q231">
         <v>3.1</v>
@@ -49676,7 +49679,7 @@
         <v>245</v>
       </c>
       <c r="P235" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q235">
         <v>2.75</v>
@@ -50500,7 +50503,7 @@
         <v>94</v>
       </c>
       <c r="P239" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q239">
         <v>3.2</v>
@@ -50990,7 +50993,7 @@
         <v>1.45</v>
       </c>
       <c r="AP241">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AQ241">
         <v>1.33</v>
@@ -51118,7 +51121,7 @@
         <v>247</v>
       </c>
       <c r="P242" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q242">
         <v>3.5</v>
@@ -51199,7 +51202,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ242">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AR242">
         <v>1.37</v>
@@ -51530,7 +51533,7 @@
         <v>224</v>
       </c>
       <c r="P244" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -51736,7 +51739,7 @@
         <v>188</v>
       </c>
       <c r="P245" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q245">
         <v>2.63</v>
@@ -51942,7 +51945,7 @@
         <v>248</v>
       </c>
       <c r="P246" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q246">
         <v>2.9</v>
@@ -52766,7 +52769,7 @@
         <v>251</v>
       </c>
       <c r="P250" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q250">
         <v>2.4</v>
@@ -52972,7 +52975,7 @@
         <v>124</v>
       </c>
       <c r="P251" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q251">
         <v>2.4</v>
@@ -53384,7 +53387,7 @@
         <v>252</v>
       </c>
       <c r="P253" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q253">
         <v>2.88</v>
@@ -53541,6 +53544,212 @@
       </c>
       <c r="BP253">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="254" spans="1:68">
+      <c r="A254" s="1">
+        <v>253</v>
+      </c>
+      <c r="B254">
+        <v>7728461</v>
+      </c>
+      <c r="C254" t="s">
+        <v>68</v>
+      </c>
+      <c r="D254" t="s">
+        <v>69</v>
+      </c>
+      <c r="E254" s="2">
+        <v>45681.6875</v>
+      </c>
+      <c r="F254">
+        <v>24</v>
+      </c>
+      <c r="G254" t="s">
+        <v>79</v>
+      </c>
+      <c r="H254" t="s">
+        <v>73</v>
+      </c>
+      <c r="I254">
+        <v>1</v>
+      </c>
+      <c r="J254">
+        <v>0</v>
+      </c>
+      <c r="K254">
+        <v>1</v>
+      </c>
+      <c r="L254">
+        <v>2</v>
+      </c>
+      <c r="M254">
+        <v>0</v>
+      </c>
+      <c r="N254">
+        <v>2</v>
+      </c>
+      <c r="O254" t="s">
+        <v>253</v>
+      </c>
+      <c r="P254" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q254">
+        <v>2.55</v>
+      </c>
+      <c r="R254">
+        <v>1.93</v>
+      </c>
+      <c r="S254">
+        <v>4.8</v>
+      </c>
+      <c r="T254">
+        <v>1.52</v>
+      </c>
+      <c r="U254">
+        <v>2.35</v>
+      </c>
+      <c r="V254">
+        <v>3.3</v>
+      </c>
+      <c r="W254">
+        <v>1.28</v>
+      </c>
+      <c r="X254">
+        <v>9.25</v>
+      </c>
+      <c r="Y254">
+        <v>1.05</v>
+      </c>
+      <c r="Z254">
+        <v>1.84</v>
+      </c>
+      <c r="AA254">
+        <v>3.45</v>
+      </c>
+      <c r="AB254">
+        <v>5</v>
+      </c>
+      <c r="AC254">
+        <v>1.11</v>
+      </c>
+      <c r="AD254">
+        <v>6.5</v>
+      </c>
+      <c r="AE254">
+        <v>1.45</v>
+      </c>
+      <c r="AF254">
+        <v>2.6</v>
+      </c>
+      <c r="AG254">
+        <v>2.37</v>
+      </c>
+      <c r="AH254">
+        <v>1.53</v>
+      </c>
+      <c r="AI254">
+        <v>2.15</v>
+      </c>
+      <c r="AJ254">
+        <v>1.61</v>
+      </c>
+      <c r="AK254">
+        <v>1.2</v>
+      </c>
+      <c r="AL254">
+        <v>1.34</v>
+      </c>
+      <c r="AM254">
+        <v>1.85</v>
+      </c>
+      <c r="AN254">
+        <v>2.17</v>
+      </c>
+      <c r="AO254">
+        <v>0.73</v>
+      </c>
+      <c r="AP254">
+        <v>2.23</v>
+      </c>
+      <c r="AQ254">
+        <v>0.67</v>
+      </c>
+      <c r="AR254">
+        <v>1.63</v>
+      </c>
+      <c r="AS254">
+        <v>1.25</v>
+      </c>
+      <c r="AT254">
+        <v>2.88</v>
+      </c>
+      <c r="AU254">
+        <v>6</v>
+      </c>
+      <c r="AV254">
+        <v>3</v>
+      </c>
+      <c r="AW254">
+        <v>12</v>
+      </c>
+      <c r="AX254">
+        <v>2</v>
+      </c>
+      <c r="AY254">
+        <v>21</v>
+      </c>
+      <c r="AZ254">
+        <v>7</v>
+      </c>
+      <c r="BA254">
+        <v>7</v>
+      </c>
+      <c r="BB254">
+        <v>2</v>
+      </c>
+      <c r="BC254">
+        <v>9</v>
+      </c>
+      <c r="BD254">
+        <v>1.47</v>
+      </c>
+      <c r="BE254">
+        <v>6.75</v>
+      </c>
+      <c r="BF254">
+        <v>3.05</v>
+      </c>
+      <c r="BG254">
+        <v>1.38</v>
+      </c>
+      <c r="BH254">
+        <v>2.7</v>
+      </c>
+      <c r="BI254">
+        <v>1.64</v>
+      </c>
+      <c r="BJ254">
+        <v>2.07</v>
+      </c>
+      <c r="BK254">
+        <v>2.02</v>
+      </c>
+      <c r="BL254">
+        <v>1.66</v>
+      </c>
+      <c r="BM254">
+        <v>2.63</v>
+      </c>
+      <c r="BN254">
+        <v>1.41</v>
+      </c>
+      <c r="BO254">
+        <v>3.4</v>
+      </c>
+      <c r="BP254">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>
